--- a/excel/II DS.xlsx
+++ b/excel/II DS.xlsx
@@ -1,10 +1,16 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <fileVersion appName="xl" lastEdited="4" lowestEdited="4" rupBuild="4505"/>
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x15="http://schemas.microsoft.com/office/spreadsheetml/2010/11/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr6="http://schemas.microsoft.com/office/spreadsheetml/2016/revision6" xmlns:xr10="http://schemas.microsoft.com/office/spreadsheetml/2016/revision10" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" mc:Ignorable="x15 xr xr6 xr10 xr2">
+  <fileVersion appName="xl" lastEdited="7" lowestEdited="4" rupBuild="30026"/>
   <workbookPr defaultThemeVersion="124226"/>
+  <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
+    <mc:Choice Requires="x15">
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\saket\Desktop\Jr Tech\Technical skills\excel\"/>
+    </mc:Choice>
+  </mc:AlternateContent>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{860B4088-85C7-4C2A-8584-5C35F1EA3E82}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="-120" yWindow="-120" windowWidth="29040" windowHeight="15840" activeTab="3"/>
+    <workbookView xWindow="0" yWindow="360" windowWidth="29040" windowHeight="15720" activeTab="3" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="DS-AA" sheetId="1" r:id="rId1"/>
@@ -864,8 +870,8 @@
 </file>
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
-<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <fonts count="17">
+<styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
+  <fonts count="18" x14ac:knownFonts="1">
     <font>
       <sz val="11"/>
       <color theme="1"/>
@@ -975,8 +981,15 @@
       <name val="Times New Roman"/>
       <family val="1"/>
     </font>
+    <font>
+      <sz val="11"/>
+      <color rgb="FF000000"/>
+      <name val="Calibri"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
-  <fills count="5">
+  <fills count="12">
     <fill>
       <patternFill patternType="none"/>
     </fill>
@@ -998,6 +1011,48 @@
     <fill>
       <patternFill patternType="solid">
         <fgColor rgb="FFFFFFFF"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="3"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="5"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFC0504D"/>
+        <bgColor rgb="FF000000"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="7" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="2" tint="-0.249977111117893"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor rgb="FFFF0000"/>
+        <bgColor indexed="64"/>
+      </patternFill>
+    </fill>
+    <fill>
+      <patternFill patternType="solid">
+        <fgColor theme="1"/>
         <bgColor indexed="64"/>
       </patternFill>
     </fill>
@@ -1169,7 +1224,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="84">
+  <cellXfs count="99">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="3" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center" vertical="center"/>
@@ -1301,9 +1356,6 @@
     <xf numFmtId="1" fontId="0" fillId="2" borderId="5" xfId="0" applyNumberFormat="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="2" borderId="4" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="left"/>
-    </xf>
     <xf numFmtId="0" fontId="12" fillId="3" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
@@ -1385,8 +1437,11 @@
     <xf numFmtId="0" fontId="10" fillId="3" borderId="12" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
       <alignment vertical="center" wrapText="1"/>
     </xf>
-    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" wrapText="1"/>
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
@@ -1394,12 +1449,39 @@
     <xf numFmtId="0" fontId="2" fillId="0" borderId="7" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="0" fillId="0" borderId="7" xfId="0" applyBorder="1" applyAlignment="1">
+    <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1" applyAlignment="1">
       <alignment horizontal="center"/>
     </xf>
-    <xf numFmtId="0" fontId="2" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1" applyAlignment="1">
-      <alignment horizontal="center" wrapText="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="3" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="center" vertical="center"/>
     </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left" vertical="center"/>
+    </xf>
+    <xf numFmtId="0" fontId="1" fillId="2" borderId="5" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment horizontal="left"/>
+    </xf>
+    <xf numFmtId="0" fontId="11" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="12" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="13" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="14" fillId="3" borderId="2" xfId="0" applyFont="1" applyFill="1" applyBorder="1" applyAlignment="1">
+      <alignment vertical="center" wrapText="1"/>
+    </xf>
+    <xf numFmtId="0" fontId="9" fillId="0" borderId="1" xfId="0" applyFont="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="5" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="6" borderId="1" xfId="0" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="17" fillId="7" borderId="1" xfId="0" applyFont="1" applyFill="1" applyBorder="1"/>
+    <xf numFmtId="0" fontId="0" fillId="8" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="9" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="10" borderId="0" xfId="0" applyFill="1"/>
+    <xf numFmtId="0" fontId="0" fillId="11" borderId="0" xfId="0" applyFill="1"/>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0"/>
@@ -5008,7 +5090,7 @@
         <xdr:cNvPr id="2" name="Picture 1" descr="C:\Users\admin\Downloads\WhatsApp Image 2022-10-20 at 10.45.51 AM.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F7D5216-6FD8-4A8F-8F37-1DDE04C15703}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{0F7D5216-6FD8-4A8F-8F37-1DDE04C15703}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5018,7 +5100,7 @@
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -5066,7 +5148,7 @@
         <xdr:cNvPr id="2" name="Picture 1" descr="C:\Users\admin\Downloads\WhatsApp Image 2022-10-20 at 10.45.51 AM.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5264CEFE-E3E5-4137-B06E-5F1B9BC0D27E}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{5264CEFE-E3E5-4137-B06E-5F1B9BC0D27E}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5076,7 +5158,7 @@
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -5124,7 +5206,7 @@
         <xdr:cNvPr id="2" name="Picture 1" descr="C:\Users\admin\Downloads\WhatsApp Image 2022-10-20 at 10.45.51 AM.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7260212E-F069-4CCB-8A8D-BE98765FD51B}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{7260212E-F069-4CCB-8A8D-BE98765FD51B}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5134,7 +5216,7 @@
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -5182,7 +5264,7 @@
         <xdr:cNvPr id="2" name="Picture 1" descr="C:\Users\admin\Downloads\WhatsApp Image 2022-10-20 at 10.45.51 AM.jpeg">
           <a:extLst>
             <a:ext uri="{FF2B5EF4-FFF2-40B4-BE49-F238E27FC236}">
-              <a16:creationId xmlns="" xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0F9E993-3BF2-469B-943C-D00B16695A37}"/>
+              <a16:creationId xmlns:a16="http://schemas.microsoft.com/office/drawing/2014/main" id="{D0F9E993-3BF2-469B-943C-D00B16695A37}"/>
             </a:ext>
           </a:extLst>
         </xdr:cNvPr>
@@ -5192,7 +5274,7 @@
         <a:blip xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:embed="rId1" cstate="print">
           <a:extLst>
             <a:ext uri="{28A0092B-C50C-407E-A947-70E740481C1C}">
-              <a14:useLocalDpi xmlns="" xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
+              <a14:useLocalDpi xmlns:a14="http://schemas.microsoft.com/office/drawing/2010/main" val="0"/>
             </a:ext>
           </a:extLst>
         </a:blip>
@@ -5221,9 +5303,9 @@
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
-<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme">
+<a:theme xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" name="Office Theme 2007 - 2010">
   <a:themeElements>
-    <a:clrScheme name="Office">
+    <a:clrScheme name="Office 2007 - 2010">
       <a:dk1>
         <a:sysClr val="windowText" lastClr="000000"/>
       </a:dk1>
@@ -5261,7 +5343,7 @@
         <a:srgbClr val="800080"/>
       </a:folHlink>
     </a:clrScheme>
-    <a:fontScheme name="Office">
+    <a:fontScheme name="Office 2007 - 2010">
       <a:majorFont>
         <a:latin typeface="Cambria"/>
         <a:ea typeface=""/>
@@ -5295,6 +5377,7 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Times New Roman"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:majorFont>
       <a:minorFont>
         <a:latin typeface="Calibri"/>
@@ -5329,9 +5412,10 @@
         <a:font script="Mong" typeface="Mongolian Baiti"/>
         <a:font script="Viet" typeface="Arial"/>
         <a:font script="Uigh" typeface="Microsoft Uighur"/>
+        <a:font script="Geor" typeface="Sylfaen"/>
       </a:minorFont>
     </a:fontScheme>
-    <a:fmtScheme name="Office">
+    <a:fmtScheme name="Office 2007 - 2010">
       <a:fillStyleLst>
         <a:solidFill>
           <a:schemeClr val="phClr"/>
@@ -5504,12 +5588,12 @@
 </file>
 
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr>
     <pageSetUpPr fitToPage="1"/>
   </sheetPr>
   <dimension ref="A1:H197"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.5703125" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
@@ -5520,15 +5604,15 @@
     <col min="7" max="7" width="49.85546875" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="61.5" customHeight="1">
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
+    <row r="1" spans="1:7" ht="61.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
       <c r="F1" s="13"/>
       <c r="G1" s="13"/>
     </row>
-    <row r="2" spans="1:7" s="32" customFormat="1" ht="27" customHeight="1">
+    <row r="2" spans="1:7" s="32" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="33"/>
       <c r="C2" s="81" t="s">
         <v>204</v>
@@ -5540,7 +5624,7 @@
         <v>205</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75">
+    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="80" t="s">
         <v>0</v>
       </c>
@@ -5551,7 +5635,7 @@
       <c r="F3" s="80"/>
       <c r="G3" s="80"/>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -5570,7 +5654,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>2024</v>
       </c>
@@ -5589,7 +5673,7 @@
         <v>7</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>2024</v>
       </c>
@@ -5608,7 +5692,7 @@
         <v>8</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>2024</v>
       </c>
@@ -5627,7 +5711,7 @@
         <v>9</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>2024</v>
       </c>
@@ -5646,7 +5730,7 @@
         <v>10</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>2024</v>
       </c>
@@ -5665,7 +5749,7 @@
         <v>11</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>2024</v>
       </c>
@@ -5684,7 +5768,7 @@
         <v>12</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>2024</v>
       </c>
@@ -5703,7 +5787,7 @@
         <v>13</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>2024</v>
       </c>
@@ -5722,7 +5806,7 @@
         <v>14</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>2024</v>
       </c>
@@ -5741,7 +5825,7 @@
         <v>15</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>2024</v>
       </c>
@@ -5760,7 +5844,7 @@
         <v>16</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>2024</v>
       </c>
@@ -5779,7 +5863,7 @@
         <v>17</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>2024</v>
       </c>
@@ -5798,7 +5882,7 @@
         <v>18</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>2024</v>
       </c>
@@ -5817,7 +5901,7 @@
         <v>19</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>2024</v>
       </c>
@@ -5836,7 +5920,7 @@
         <v>20</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>2024</v>
       </c>
@@ -5855,7 +5939,7 @@
         <v>21</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>2024</v>
       </c>
@@ -5874,7 +5958,7 @@
         <v>22</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>2024</v>
       </c>
@@ -5893,7 +5977,7 @@
         <v>23</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>2024</v>
       </c>
@@ -5912,7 +5996,7 @@
         <v>24</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>2024</v>
       </c>
@@ -5931,7 +6015,7 @@
         <v>25</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>2024</v>
       </c>
@@ -5950,7 +6034,7 @@
         <v>26</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>2024</v>
       </c>
@@ -5969,7 +6053,7 @@
         <v>27</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>2024</v>
       </c>
@@ -5988,7 +6072,7 @@
         <v>28</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>2024</v>
       </c>
@@ -6007,7 +6091,7 @@
         <v>29</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>2024</v>
       </c>
@@ -6026,7 +6110,7 @@
         <v>30</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>2024</v>
       </c>
@@ -6045,7 +6129,7 @@
         <v>31</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>2024</v>
       </c>
@@ -6064,7 +6148,7 @@
         <v>32</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>2024</v>
       </c>
@@ -6083,7 +6167,7 @@
         <v>33</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>2024</v>
       </c>
@@ -6102,7 +6186,7 @@
         <v>34</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>2024</v>
       </c>
@@ -6121,7 +6205,7 @@
         <v>35</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>2024</v>
       </c>
@@ -6140,7 +6224,7 @@
         <v>36</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>2024</v>
       </c>
@@ -6159,7 +6243,7 @@
         <v>37</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>2024</v>
       </c>
@@ -6178,7 +6262,7 @@
         <v>38</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>2024</v>
       </c>
@@ -6197,7 +6281,7 @@
         <v>39</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>2024</v>
       </c>
@@ -6216,7 +6300,7 @@
         <v>40</v>
       </c>
     </row>
-    <row r="39" spans="1:8">
+    <row r="39" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>2024</v>
       </c>
@@ -6235,7 +6319,7 @@
         <v>41</v>
       </c>
     </row>
-    <row r="40" spans="1:8">
+    <row r="40" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>2024</v>
       </c>
@@ -6254,7 +6338,7 @@
         <v>42</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>2024</v>
       </c>
@@ -6273,7 +6357,7 @@
         <v>43</v>
       </c>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>2024</v>
       </c>
@@ -6296,7 +6380,7 @@
         <v>46</v>
       </c>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>2024</v>
       </c>
@@ -6315,7 +6399,7 @@
         <v>47</v>
       </c>
     </row>
-    <row r="44" spans="1:8" ht="15.75">
+    <row r="44" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A44" s="21"/>
       <c r="B44" s="37">
         <v>40</v>
@@ -6335,7 +6419,7 @@
         <v>215</v>
       </c>
     </row>
-    <row r="45" spans="1:8" ht="15.75">
+    <row r="45" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A45" s="21"/>
       <c r="B45" s="37">
         <v>41</v>
@@ -6355,7 +6439,7 @@
         <v>218</v>
       </c>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="21"/>
       <c r="B46" s="37">
         <v>42</v>
@@ -6365,17 +6449,17 @@
       </c>
       <c r="D46" s="37"/>
       <c r="E46" s="37"/>
-      <c r="F46" s="68">
+      <c r="F46" s="67">
         <v>241641101009</v>
       </c>
-      <c r="G46" s="66" t="s">
+      <c r="G46" s="65" t="s">
         <v>234</v>
       </c>
       <c r="H46" s="40" t="s">
         <v>235</v>
       </c>
     </row>
-    <row r="47" spans="1:8" ht="15.75">
+    <row r="47" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A47" s="21"/>
       <c r="B47" s="37">
         <v>43</v>
@@ -6395,7 +6479,7 @@
         <v>242</v>
       </c>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="21"/>
       <c r="B48" s="22"/>
       <c r="C48" s="22"/>
@@ -6404,7 +6488,7 @@
       <c r="F48" s="25"/>
       <c r="G48" s="26"/>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="21"/>
       <c r="B49" s="22"/>
       <c r="C49" s="22"/>
@@ -6413,7 +6497,7 @@
       <c r="F49" s="25"/>
       <c r="G49" s="26"/>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="21"/>
       <c r="B50" s="22"/>
       <c r="C50" s="22"/>
@@ -6422,7 +6506,7 @@
       <c r="F50" s="25"/>
       <c r="G50" s="26"/>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="21"/>
       <c r="B51" s="22"/>
       <c r="C51" s="22"/>
@@ -6431,7 +6515,7 @@
       <c r="F51" s="25"/>
       <c r="G51" s="26"/>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="21"/>
       <c r="B52" s="22"/>
       <c r="C52" s="22"/>
@@ -6440,7 +6524,7 @@
       <c r="F52" s="25"/>
       <c r="G52" s="26"/>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="21"/>
       <c r="B53" s="22"/>
       <c r="C53" s="22"/>
@@ -6449,7 +6533,7 @@
       <c r="F53" s="25"/>
       <c r="G53" s="26"/>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="21"/>
       <c r="B54" s="22"/>
       <c r="C54" s="22"/>
@@ -6458,7 +6542,7 @@
       <c r="F54" s="25"/>
       <c r="G54" s="26"/>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="21"/>
       <c r="B55" s="22"/>
       <c r="C55" s="22"/>
@@ -6467,7 +6551,7 @@
       <c r="F55" s="25"/>
       <c r="G55" s="26"/>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="21"/>
       <c r="B56" s="22"/>
       <c r="C56" s="22"/>
@@ -6476,7 +6560,7 @@
       <c r="F56" s="25"/>
       <c r="G56" s="26"/>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="21"/>
       <c r="B57" s="22"/>
       <c r="C57" s="22"/>
@@ -6485,7 +6569,7 @@
       <c r="F57" s="25"/>
       <c r="G57" s="26"/>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="21"/>
       <c r="B58" s="22"/>
       <c r="C58" s="22"/>
@@ -6494,7 +6578,7 @@
       <c r="F58" s="25"/>
       <c r="G58" s="26"/>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="21"/>
       <c r="B59" s="22"/>
       <c r="C59" s="22"/>
@@ -6503,7 +6587,7 @@
       <c r="F59" s="25"/>
       <c r="G59" s="26"/>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="21"/>
       <c r="B60" s="22"/>
       <c r="C60" s="22"/>
@@ -6512,7 +6596,7 @@
       <c r="F60" s="25"/>
       <c r="G60" s="26"/>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="21"/>
       <c r="B61" s="22"/>
       <c r="C61" s="22"/>
@@ -6521,7 +6605,7 @@
       <c r="F61" s="25"/>
       <c r="G61" s="26"/>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="21"/>
       <c r="B62" s="22"/>
       <c r="C62" s="22"/>
@@ -6530,7 +6614,7 @@
       <c r="F62" s="25"/>
       <c r="G62" s="26"/>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="21"/>
       <c r="B63" s="22"/>
       <c r="C63" s="22"/>
@@ -6539,7 +6623,7 @@
       <c r="F63" s="25"/>
       <c r="G63" s="26"/>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="21"/>
       <c r="B64" s="22"/>
       <c r="C64" s="22"/>
@@ -6548,7 +6632,7 @@
       <c r="F64" s="25"/>
       <c r="G64" s="26"/>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="21"/>
       <c r="B65" s="22"/>
       <c r="C65" s="22"/>
@@ -6557,7 +6641,7 @@
       <c r="F65" s="25"/>
       <c r="G65" s="26"/>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="21"/>
       <c r="B66" s="22"/>
       <c r="C66" s="22"/>
@@ -6566,7 +6650,7 @@
       <c r="F66" s="25"/>
       <c r="G66" s="26"/>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="21"/>
       <c r="B67" s="22"/>
       <c r="C67" s="22"/>
@@ -6575,7 +6659,7 @@
       <c r="F67" s="25"/>
       <c r="G67" s="26"/>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="21"/>
       <c r="B68" s="22"/>
       <c r="C68" s="22"/>
@@ -6584,7 +6668,7 @@
       <c r="F68" s="25"/>
       <c r="G68" s="26"/>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="21"/>
       <c r="B69" s="22"/>
       <c r="C69" s="22"/>
@@ -6593,7 +6677,7 @@
       <c r="F69" s="25"/>
       <c r="G69" s="26"/>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="21"/>
       <c r="B70" s="22"/>
       <c r="C70" s="22"/>
@@ -6602,7 +6686,7 @@
       <c r="F70" s="25"/>
       <c r="G70" s="26"/>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="21"/>
       <c r="B71" s="22"/>
       <c r="C71" s="22"/>
@@ -6611,7 +6695,7 @@
       <c r="F71" s="25"/>
       <c r="G71" s="26"/>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="21"/>
       <c r="B72" s="22"/>
       <c r="C72" s="22"/>
@@ -6620,7 +6704,7 @@
       <c r="F72" s="25"/>
       <c r="G72" s="26"/>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="21"/>
       <c r="B73" s="22"/>
       <c r="C73" s="22"/>
@@ -6629,7 +6713,7 @@
       <c r="F73" s="25"/>
       <c r="G73" s="26"/>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="21"/>
       <c r="B74" s="22"/>
       <c r="C74" s="22"/>
@@ -6638,7 +6722,7 @@
       <c r="F74" s="25"/>
       <c r="G74" s="26"/>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="21"/>
       <c r="B75" s="22"/>
       <c r="C75" s="22"/>
@@ -6647,7 +6731,7 @@
       <c r="F75" s="25"/>
       <c r="G75" s="26"/>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="21"/>
       <c r="B76" s="22"/>
       <c r="C76" s="22"/>
@@ -6656,7 +6740,7 @@
       <c r="F76" s="25"/>
       <c r="G76" s="26"/>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="21"/>
       <c r="B77" s="22"/>
       <c r="C77" s="22"/>
@@ -6665,7 +6749,7 @@
       <c r="F77" s="25"/>
       <c r="G77" s="26"/>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="21"/>
       <c r="B78" s="22"/>
       <c r="C78" s="22"/>
@@ -6674,7 +6758,7 @@
       <c r="F78" s="25"/>
       <c r="G78" s="26"/>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="21"/>
       <c r="B79" s="22"/>
       <c r="C79" s="22"/>
@@ -6683,7 +6767,7 @@
       <c r="F79" s="24"/>
       <c r="G79" s="24"/>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="21"/>
       <c r="B80" s="22"/>
       <c r="C80" s="22"/>
@@ -6692,7 +6776,7 @@
       <c r="F80" s="25"/>
       <c r="G80" s="27"/>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="21"/>
       <c r="B81" s="22"/>
       <c r="C81" s="22"/>
@@ -6701,7 +6785,7 @@
       <c r="F81" s="25"/>
       <c r="G81" s="27"/>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="21"/>
       <c r="B82" s="22"/>
       <c r="C82" s="22"/>
@@ -6710,7 +6794,7 @@
       <c r="F82" s="25"/>
       <c r="G82" s="27"/>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="21"/>
       <c r="B83" s="22"/>
       <c r="C83" s="22"/>
@@ -6719,7 +6803,7 @@
       <c r="F83" s="25"/>
       <c r="G83" s="27"/>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="21"/>
       <c r="B84" s="22"/>
       <c r="C84" s="22"/>
@@ -6728,7 +6812,7 @@
       <c r="F84" s="25"/>
       <c r="G84" s="27"/>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="21"/>
       <c r="B85" s="22"/>
       <c r="C85" s="22"/>
@@ -6737,7 +6821,7 @@
       <c r="F85" s="25"/>
       <c r="G85" s="27"/>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="21"/>
       <c r="B86" s="22"/>
       <c r="C86" s="22"/>
@@ -6746,7 +6830,7 @@
       <c r="F86" s="25"/>
       <c r="G86" s="27"/>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="21"/>
       <c r="B87" s="22"/>
       <c r="C87" s="22"/>
@@ -6755,7 +6839,7 @@
       <c r="F87" s="25"/>
       <c r="G87" s="27"/>
     </row>
-    <row r="88" spans="1:7">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="21"/>
       <c r="B88" s="22"/>
       <c r="C88" s="22"/>
@@ -6764,7 +6848,7 @@
       <c r="F88" s="25"/>
       <c r="G88" s="27"/>
     </row>
-    <row r="89" spans="1:7">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="21"/>
       <c r="B89" s="22"/>
       <c r="C89" s="22"/>
@@ -6773,7 +6857,7 @@
       <c r="F89" s="25"/>
       <c r="G89" s="27"/>
     </row>
-    <row r="90" spans="1:7">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="21"/>
       <c r="B90" s="22"/>
       <c r="C90" s="22"/>
@@ -6782,7 +6866,7 @@
       <c r="F90" s="25"/>
       <c r="G90" s="27"/>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="21"/>
       <c r="B91" s="22"/>
       <c r="C91" s="22"/>
@@ -6791,7 +6875,7 @@
       <c r="F91" s="25"/>
       <c r="G91" s="27"/>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="21"/>
       <c r="B92" s="22"/>
       <c r="C92" s="22"/>
@@ -6800,7 +6884,7 @@
       <c r="F92" s="25"/>
       <c r="G92" s="27"/>
     </row>
-    <row r="93" spans="1:7">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="21"/>
       <c r="B93" s="22"/>
       <c r="C93" s="22"/>
@@ -6809,7 +6893,7 @@
       <c r="F93" s="25"/>
       <c r="G93" s="27"/>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="21"/>
       <c r="B94" s="22"/>
       <c r="C94" s="22"/>
@@ -6818,7 +6902,7 @@
       <c r="F94" s="25"/>
       <c r="G94" s="27"/>
     </row>
-    <row r="95" spans="1:7">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="21"/>
       <c r="B95" s="22"/>
       <c r="C95" s="22"/>
@@ -6827,7 +6911,7 @@
       <c r="F95" s="25"/>
       <c r="G95" s="27"/>
     </row>
-    <row r="96" spans="1:7">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="21"/>
       <c r="B96" s="22"/>
       <c r="C96" s="22"/>
@@ -6836,7 +6920,7 @@
       <c r="F96" s="25"/>
       <c r="G96" s="27"/>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="21"/>
       <c r="B97" s="22"/>
       <c r="C97" s="22"/>
@@ -6845,7 +6929,7 @@
       <c r="F97" s="25"/>
       <c r="G97" s="27"/>
     </row>
-    <row r="98" spans="1:7">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="21"/>
       <c r="B98" s="22"/>
       <c r="C98" s="22"/>
@@ -6854,7 +6938,7 @@
       <c r="F98" s="25"/>
       <c r="G98" s="27"/>
     </row>
-    <row r="99" spans="1:7">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="21"/>
       <c r="B99" s="22"/>
       <c r="C99" s="22"/>
@@ -6863,7 +6947,7 @@
       <c r="F99" s="25"/>
       <c r="G99" s="27"/>
     </row>
-    <row r="100" spans="1:7">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="21"/>
       <c r="B100" s="22"/>
       <c r="C100" s="22"/>
@@ -6872,7 +6956,7 @@
       <c r="F100" s="25"/>
       <c r="G100" s="27"/>
     </row>
-    <row r="101" spans="1:7">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="21"/>
       <c r="B101" s="22"/>
       <c r="C101" s="22"/>
@@ -6881,7 +6965,7 @@
       <c r="F101" s="25"/>
       <c r="G101" s="27"/>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="21"/>
       <c r="B102" s="22"/>
       <c r="C102" s="22"/>
@@ -6890,7 +6974,7 @@
       <c r="F102" s="25"/>
       <c r="G102" s="27"/>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="21"/>
       <c r="B103" s="22"/>
       <c r="C103" s="22"/>
@@ -6899,7 +6983,7 @@
       <c r="F103" s="25"/>
       <c r="G103" s="27"/>
     </row>
-    <row r="104" spans="1:7">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="21"/>
       <c r="B104" s="22"/>
       <c r="C104" s="22"/>
@@ -6908,7 +6992,7 @@
       <c r="F104" s="25"/>
       <c r="G104" s="27"/>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="21"/>
       <c r="B105" s="22"/>
       <c r="C105" s="22"/>
@@ -6917,7 +7001,7 @@
       <c r="F105" s="25"/>
       <c r="G105" s="27"/>
     </row>
-    <row r="106" spans="1:7">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="21"/>
       <c r="B106" s="22"/>
       <c r="C106" s="22"/>
@@ -6926,7 +7010,7 @@
       <c r="F106" s="25"/>
       <c r="G106" s="27"/>
     </row>
-    <row r="107" spans="1:7">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="21"/>
       <c r="B107" s="22"/>
       <c r="C107" s="22"/>
@@ -6935,7 +7019,7 @@
       <c r="F107" s="25"/>
       <c r="G107" s="27"/>
     </row>
-    <row r="108" spans="1:7">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="21"/>
       <c r="B108" s="22"/>
       <c r="C108" s="22"/>
@@ -6944,7 +7028,7 @@
       <c r="F108" s="25"/>
       <c r="G108" s="27"/>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="21"/>
       <c r="B109" s="22"/>
       <c r="C109" s="22"/>
@@ -6953,7 +7037,7 @@
       <c r="F109" s="25"/>
       <c r="G109" s="27"/>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="21"/>
       <c r="B110" s="22"/>
       <c r="C110" s="22"/>
@@ -6962,7 +7046,7 @@
       <c r="F110" s="25"/>
       <c r="G110" s="27"/>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="21"/>
       <c r="B111" s="22"/>
       <c r="C111" s="22"/>
@@ -6971,7 +7055,7 @@
       <c r="F111" s="25"/>
       <c r="G111" s="27"/>
     </row>
-    <row r="112" spans="1:7">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="21"/>
       <c r="B112" s="22"/>
       <c r="C112" s="22"/>
@@ -6980,7 +7064,7 @@
       <c r="F112" s="25"/>
       <c r="G112" s="27"/>
     </row>
-    <row r="113" spans="1:7">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="21"/>
       <c r="B113" s="22"/>
       <c r="C113" s="22"/>
@@ -6989,7 +7073,7 @@
       <c r="F113" s="25"/>
       <c r="G113" s="27"/>
     </row>
-    <row r="114" spans="1:7">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="21"/>
       <c r="B114" s="22"/>
       <c r="C114" s="22"/>
@@ -6998,7 +7082,7 @@
       <c r="F114" s="25"/>
       <c r="G114" s="27"/>
     </row>
-    <row r="115" spans="1:7">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="21"/>
       <c r="B115" s="22"/>
       <c r="C115" s="22"/>
@@ -7007,7 +7091,7 @@
       <c r="F115" s="25"/>
       <c r="G115" s="27"/>
     </row>
-    <row r="116" spans="1:7">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="21"/>
       <c r="B116" s="22"/>
       <c r="C116" s="22"/>
@@ -7016,7 +7100,7 @@
       <c r="F116" s="25"/>
       <c r="G116" s="27"/>
     </row>
-    <row r="117" spans="1:7">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="21"/>
       <c r="B117" s="22"/>
       <c r="C117" s="22"/>
@@ -7025,7 +7109,7 @@
       <c r="F117" s="25"/>
       <c r="G117" s="27"/>
     </row>
-    <row r="118" spans="1:7">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="21"/>
       <c r="B118" s="22"/>
       <c r="C118" s="22"/>
@@ -7034,7 +7118,7 @@
       <c r="F118" s="25"/>
       <c r="G118" s="27"/>
     </row>
-    <row r="119" spans="1:7">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="21"/>
       <c r="B119" s="22"/>
       <c r="C119" s="22"/>
@@ -7043,7 +7127,7 @@
       <c r="F119" s="25"/>
       <c r="G119" s="27"/>
     </row>
-    <row r="120" spans="1:7">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="21"/>
       <c r="B120" s="22"/>
       <c r="C120" s="22"/>
@@ -7052,7 +7136,7 @@
       <c r="F120" s="25"/>
       <c r="G120" s="27"/>
     </row>
-    <row r="121" spans="1:7">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="21"/>
       <c r="B121" s="22"/>
       <c r="C121" s="22"/>
@@ -7061,7 +7145,7 @@
       <c r="F121" s="25"/>
       <c r="G121" s="27"/>
     </row>
-    <row r="122" spans="1:7">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="21"/>
       <c r="B122" s="22"/>
       <c r="C122" s="22"/>
@@ -7070,7 +7154,7 @@
       <c r="F122" s="25"/>
       <c r="G122" s="27"/>
     </row>
-    <row r="123" spans="1:7">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="21"/>
       <c r="B123" s="22"/>
       <c r="C123" s="22"/>
@@ -7079,7 +7163,7 @@
       <c r="F123" s="25"/>
       <c r="G123" s="27"/>
     </row>
-    <row r="124" spans="1:7">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="21"/>
       <c r="B124" s="22"/>
       <c r="C124" s="22"/>
@@ -7088,7 +7172,7 @@
       <c r="F124" s="25"/>
       <c r="G124" s="27"/>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="21"/>
       <c r="B125" s="22"/>
       <c r="C125" s="22"/>
@@ -7097,7 +7181,7 @@
       <c r="F125" s="25"/>
       <c r="G125" s="27"/>
     </row>
-    <row r="126" spans="1:7">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="21"/>
       <c r="B126" s="22"/>
       <c r="C126" s="22"/>
@@ -7106,7 +7190,7 @@
       <c r="F126" s="25"/>
       <c r="G126" s="27"/>
     </row>
-    <row r="127" spans="1:7">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="21"/>
       <c r="B127" s="22"/>
       <c r="C127" s="22"/>
@@ -7115,7 +7199,7 @@
       <c r="F127" s="25"/>
       <c r="G127" s="27"/>
     </row>
-    <row r="128" spans="1:7">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="21"/>
       <c r="B128" s="22"/>
       <c r="C128" s="22"/>
@@ -7124,7 +7208,7 @@
       <c r="F128" s="25"/>
       <c r="G128" s="27"/>
     </row>
-    <row r="129" spans="1:7">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="21"/>
       <c r="B129" s="22"/>
       <c r="C129" s="22"/>
@@ -7133,7 +7217,7 @@
       <c r="F129" s="25"/>
       <c r="G129" s="27"/>
     </row>
-    <row r="130" spans="1:7">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="21"/>
       <c r="B130" s="22"/>
       <c r="C130" s="22"/>
@@ -7142,7 +7226,7 @@
       <c r="F130" s="25"/>
       <c r="G130" s="27"/>
     </row>
-    <row r="131" spans="1:7">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="21"/>
       <c r="B131" s="22"/>
       <c r="C131" s="22"/>
@@ -7151,7 +7235,7 @@
       <c r="F131" s="25"/>
       <c r="G131" s="27"/>
     </row>
-    <row r="132" spans="1:7">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="21"/>
       <c r="B132" s="22"/>
       <c r="C132" s="22"/>
@@ -7160,7 +7244,7 @@
       <c r="F132" s="25"/>
       <c r="G132" s="27"/>
     </row>
-    <row r="133" spans="1:7">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="21"/>
       <c r="B133" s="22"/>
       <c r="C133" s="22"/>
@@ -7169,7 +7253,7 @@
       <c r="F133" s="25"/>
       <c r="G133" s="27"/>
     </row>
-    <row r="134" spans="1:7">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="21"/>
       <c r="B134" s="22"/>
       <c r="C134" s="22"/>
@@ -7178,7 +7262,7 @@
       <c r="F134" s="25"/>
       <c r="G134" s="27"/>
     </row>
-    <row r="135" spans="1:7">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="21"/>
       <c r="B135" s="22"/>
       <c r="C135" s="22"/>
@@ -7187,7 +7271,7 @@
       <c r="F135" s="25"/>
       <c r="G135" s="27"/>
     </row>
-    <row r="136" spans="1:7">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="21"/>
       <c r="B136" s="22"/>
       <c r="C136" s="22"/>
@@ -7196,7 +7280,7 @@
       <c r="F136" s="25"/>
       <c r="G136" s="27"/>
     </row>
-    <row r="137" spans="1:7">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="21"/>
       <c r="B137" s="22"/>
       <c r="C137" s="22"/>
@@ -7205,7 +7289,7 @@
       <c r="F137" s="25"/>
       <c r="G137" s="27"/>
     </row>
-    <row r="138" spans="1:7">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="21"/>
       <c r="B138" s="22"/>
       <c r="C138" s="22"/>
@@ -7214,7 +7298,7 @@
       <c r="F138" s="25"/>
       <c r="G138" s="27"/>
     </row>
-    <row r="139" spans="1:7">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="21"/>
       <c r="B139" s="22"/>
       <c r="C139" s="22"/>
@@ -7223,7 +7307,7 @@
       <c r="F139" s="29"/>
       <c r="G139" s="27"/>
     </row>
-    <row r="140" spans="1:7">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="21"/>
       <c r="B140" s="22"/>
       <c r="C140" s="22"/>
@@ -7232,7 +7316,7 @@
       <c r="F140" s="25"/>
       <c r="G140" s="27"/>
     </row>
-    <row r="141" spans="1:7">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="21"/>
       <c r="B141" s="22"/>
       <c r="C141" s="22"/>
@@ -7241,7 +7325,7 @@
       <c r="F141" s="24"/>
       <c r="G141" s="24"/>
     </row>
-    <row r="142" spans="1:7">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="21"/>
       <c r="B142" s="22"/>
       <c r="C142" s="22"/>
@@ -7250,7 +7334,7 @@
       <c r="F142" s="25"/>
       <c r="G142" s="27"/>
     </row>
-    <row r="143" spans="1:7">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="21"/>
       <c r="B143" s="22"/>
       <c r="C143" s="22"/>
@@ -7259,7 +7343,7 @@
       <c r="F143" s="25"/>
       <c r="G143" s="27"/>
     </row>
-    <row r="144" spans="1:7">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="21"/>
       <c r="B144" s="22"/>
       <c r="C144" s="22"/>
@@ -7268,7 +7352,7 @@
       <c r="F144" s="25"/>
       <c r="G144" s="27"/>
     </row>
-    <row r="145" spans="1:7">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="21"/>
       <c r="B145" s="22"/>
       <c r="C145" s="22"/>
@@ -7277,7 +7361,7 @@
       <c r="F145" s="25"/>
       <c r="G145" s="27"/>
     </row>
-    <row r="146" spans="1:7">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="21"/>
       <c r="B146" s="22"/>
       <c r="C146" s="22"/>
@@ -7286,7 +7370,7 @@
       <c r="F146" s="25"/>
       <c r="G146" s="27"/>
     </row>
-    <row r="147" spans="1:7">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="21"/>
       <c r="B147" s="22"/>
       <c r="C147" s="22"/>
@@ -7295,7 +7379,7 @@
       <c r="F147" s="25"/>
       <c r="G147" s="27"/>
     </row>
-    <row r="148" spans="1:7">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="21"/>
       <c r="B148" s="22"/>
       <c r="C148" s="22"/>
@@ -7304,7 +7388,7 @@
       <c r="F148" s="25"/>
       <c r="G148" s="27"/>
     </row>
-    <row r="149" spans="1:7">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="21"/>
       <c r="B149" s="22"/>
       <c r="C149" s="22"/>
@@ -7313,7 +7397,7 @@
       <c r="F149" s="25"/>
       <c r="G149" s="27"/>
     </row>
-    <row r="150" spans="1:7">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="21"/>
       <c r="B150" s="22"/>
       <c r="C150" s="22"/>
@@ -7322,7 +7406,7 @@
       <c r="F150" s="25"/>
       <c r="G150" s="27"/>
     </row>
-    <row r="151" spans="1:7">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="21"/>
       <c r="B151" s="22"/>
       <c r="C151" s="22"/>
@@ -7331,7 +7415,7 @@
       <c r="F151" s="25"/>
       <c r="G151" s="27"/>
     </row>
-    <row r="152" spans="1:7">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="21"/>
       <c r="B152" s="22"/>
       <c r="C152" s="22"/>
@@ -7340,7 +7424,7 @@
       <c r="F152" s="25"/>
       <c r="G152" s="27"/>
     </row>
-    <row r="153" spans="1:7">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="21"/>
       <c r="B153" s="22"/>
       <c r="C153" s="22"/>
@@ -7349,7 +7433,7 @@
       <c r="F153" s="25"/>
       <c r="G153" s="27"/>
     </row>
-    <row r="154" spans="1:7">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="21"/>
       <c r="B154" s="22"/>
       <c r="C154" s="22"/>
@@ -7358,7 +7442,7 @@
       <c r="F154" s="25"/>
       <c r="G154" s="27"/>
     </row>
-    <row r="155" spans="1:7">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="21"/>
       <c r="B155" s="22"/>
       <c r="C155" s="22"/>
@@ -7367,7 +7451,7 @@
       <c r="F155" s="25"/>
       <c r="G155" s="27"/>
     </row>
-    <row r="156" spans="1:7">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="21"/>
       <c r="B156" s="22"/>
       <c r="C156" s="22"/>
@@ -7376,7 +7460,7 @@
       <c r="F156" s="25"/>
       <c r="G156" s="27"/>
     </row>
-    <row r="157" spans="1:7">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="21"/>
       <c r="B157" s="22"/>
       <c r="C157" s="22"/>
@@ -7385,7 +7469,7 @@
       <c r="F157" s="25"/>
       <c r="G157" s="27"/>
     </row>
-    <row r="158" spans="1:7">
+    <row r="158" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A158" s="21"/>
       <c r="B158" s="22"/>
       <c r="C158" s="22"/>
@@ -7394,7 +7478,7 @@
       <c r="F158" s="25"/>
       <c r="G158" s="27"/>
     </row>
-    <row r="159" spans="1:7">
+    <row r="159" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A159" s="21"/>
       <c r="B159" s="22"/>
       <c r="C159" s="22"/>
@@ -7403,7 +7487,7 @@
       <c r="F159" s="25"/>
       <c r="G159" s="27"/>
     </row>
-    <row r="160" spans="1:7">
+    <row r="160" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A160" s="21"/>
       <c r="B160" s="22"/>
       <c r="C160" s="22"/>
@@ -7412,7 +7496,7 @@
       <c r="F160" s="25"/>
       <c r="G160" s="27"/>
     </row>
-    <row r="161" spans="1:7">
+    <row r="161" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A161" s="21"/>
       <c r="B161" s="22"/>
       <c r="C161" s="22"/>
@@ -7421,7 +7505,7 @@
       <c r="F161" s="25"/>
       <c r="G161" s="27"/>
     </row>
-    <row r="162" spans="1:7">
+    <row r="162" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A162" s="21"/>
       <c r="B162" s="22"/>
       <c r="C162" s="22"/>
@@ -7430,7 +7514,7 @@
       <c r="F162" s="25"/>
       <c r="G162" s="27"/>
     </row>
-    <row r="163" spans="1:7">
+    <row r="163" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A163" s="21"/>
       <c r="B163" s="22"/>
       <c r="C163" s="22"/>
@@ -7439,7 +7523,7 @@
       <c r="F163" s="25"/>
       <c r="G163" s="27"/>
     </row>
-    <row r="164" spans="1:7">
+    <row r="164" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A164" s="21"/>
       <c r="B164" s="22"/>
       <c r="C164" s="22"/>
@@ -7448,7 +7532,7 @@
       <c r="F164" s="25"/>
       <c r="G164" s="27"/>
     </row>
-    <row r="165" spans="1:7">
+    <row r="165" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A165" s="21"/>
       <c r="B165" s="22"/>
       <c r="C165" s="22"/>
@@ -7457,7 +7541,7 @@
       <c r="F165" s="25"/>
       <c r="G165" s="27"/>
     </row>
-    <row r="166" spans="1:7">
+    <row r="166" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A166" s="21"/>
       <c r="B166" s="22"/>
       <c r="C166" s="22"/>
@@ -7466,7 +7550,7 @@
       <c r="F166" s="25"/>
       <c r="G166" s="27"/>
     </row>
-    <row r="167" spans="1:7">
+    <row r="167" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A167" s="21"/>
       <c r="B167" s="22"/>
       <c r="C167" s="22"/>
@@ -7475,7 +7559,7 @@
       <c r="F167" s="25"/>
       <c r="G167" s="27"/>
     </row>
-    <row r="168" spans="1:7">
+    <row r="168" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A168" s="21"/>
       <c r="B168" s="22"/>
       <c r="C168" s="22"/>
@@ -7484,7 +7568,7 @@
       <c r="F168" s="25"/>
       <c r="G168" s="27"/>
     </row>
-    <row r="169" spans="1:7">
+    <row r="169" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A169" s="21"/>
       <c r="B169" s="22"/>
       <c r="C169" s="22"/>
@@ -7493,7 +7577,7 @@
       <c r="F169" s="25"/>
       <c r="G169" s="27"/>
     </row>
-    <row r="170" spans="1:7">
+    <row r="170" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A170" s="21"/>
       <c r="B170" s="22"/>
       <c r="C170" s="22"/>
@@ -7502,7 +7586,7 @@
       <c r="F170" s="25"/>
       <c r="G170" s="27"/>
     </row>
-    <row r="171" spans="1:7">
+    <row r="171" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A171" s="21"/>
       <c r="B171" s="22"/>
       <c r="C171" s="22"/>
@@ -7511,7 +7595,7 @@
       <c r="F171" s="25"/>
       <c r="G171" s="27"/>
     </row>
-    <row r="172" spans="1:7">
+    <row r="172" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A172" s="21"/>
       <c r="B172" s="22"/>
       <c r="C172" s="22"/>
@@ -7520,7 +7604,7 @@
       <c r="F172" s="25"/>
       <c r="G172" s="27"/>
     </row>
-    <row r="173" spans="1:7">
+    <row r="173" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A173" s="21"/>
       <c r="B173" s="22"/>
       <c r="C173" s="22"/>
@@ -7529,7 +7613,7 @@
       <c r="F173" s="25"/>
       <c r="G173" s="27"/>
     </row>
-    <row r="174" spans="1:7">
+    <row r="174" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A174" s="21"/>
       <c r="B174" s="22"/>
       <c r="C174" s="22"/>
@@ -7538,7 +7622,7 @@
       <c r="F174" s="25"/>
       <c r="G174" s="27"/>
     </row>
-    <row r="175" spans="1:7">
+    <row r="175" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A175" s="21"/>
       <c r="B175" s="22"/>
       <c r="C175" s="22"/>
@@ -7547,7 +7631,7 @@
       <c r="F175" s="25"/>
       <c r="G175" s="27"/>
     </row>
-    <row r="176" spans="1:7">
+    <row r="176" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A176" s="21"/>
       <c r="B176" s="22"/>
       <c r="C176" s="22"/>
@@ -7556,7 +7640,7 @@
       <c r="F176" s="25"/>
       <c r="G176" s="27"/>
     </row>
-    <row r="177" spans="1:7">
+    <row r="177" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A177" s="21"/>
       <c r="B177" s="22"/>
       <c r="C177" s="22"/>
@@ -7565,7 +7649,7 @@
       <c r="F177" s="25"/>
       <c r="G177" s="27"/>
     </row>
-    <row r="178" spans="1:7">
+    <row r="178" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A178" s="21"/>
       <c r="B178" s="22"/>
       <c r="C178" s="22"/>
@@ -7574,7 +7658,7 @@
       <c r="F178" s="25"/>
       <c r="G178" s="27"/>
     </row>
-    <row r="179" spans="1:7">
+    <row r="179" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A179" s="21"/>
       <c r="B179" s="22"/>
       <c r="C179" s="22"/>
@@ -7583,7 +7667,7 @@
       <c r="F179" s="25"/>
       <c r="G179" s="27"/>
     </row>
-    <row r="180" spans="1:7">
+    <row r="180" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A180" s="21"/>
       <c r="B180" s="22"/>
       <c r="C180" s="22"/>
@@ -7592,7 +7676,7 @@
       <c r="F180" s="25"/>
       <c r="G180" s="27"/>
     </row>
-    <row r="181" spans="1:7">
+    <row r="181" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A181" s="21"/>
       <c r="B181" s="22"/>
       <c r="C181" s="22"/>
@@ -7601,7 +7685,7 @@
       <c r="F181" s="25"/>
       <c r="G181" s="27"/>
     </row>
-    <row r="182" spans="1:7">
+    <row r="182" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A182" s="21"/>
       <c r="B182" s="22"/>
       <c r="C182" s="22"/>
@@ -7610,7 +7694,7 @@
       <c r="F182" s="25"/>
       <c r="G182" s="27"/>
     </row>
-    <row r="183" spans="1:7">
+    <row r="183" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A183" s="21"/>
       <c r="B183" s="22"/>
       <c r="C183" s="22"/>
@@ -7619,7 +7703,7 @@
       <c r="F183" s="25"/>
       <c r="G183" s="27"/>
     </row>
-    <row r="184" spans="1:7">
+    <row r="184" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A184" s="21"/>
       <c r="B184" s="22"/>
       <c r="C184" s="22"/>
@@ -7628,7 +7712,7 @@
       <c r="F184" s="25"/>
       <c r="G184" s="27"/>
     </row>
-    <row r="185" spans="1:7">
+    <row r="185" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A185" s="21"/>
       <c r="B185" s="22"/>
       <c r="C185" s="22"/>
@@ -7637,7 +7721,7 @@
       <c r="F185" s="25"/>
       <c r="G185" s="27"/>
     </row>
-    <row r="186" spans="1:7">
+    <row r="186" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A186" s="21"/>
       <c r="B186" s="22"/>
       <c r="C186" s="22"/>
@@ -7646,7 +7730,7 @@
       <c r="F186" s="25"/>
       <c r="G186" s="27"/>
     </row>
-    <row r="187" spans="1:7">
+    <row r="187" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A187" s="21"/>
       <c r="B187" s="22"/>
       <c r="C187" s="22"/>
@@ -7655,7 +7739,7 @@
       <c r="F187" s="25"/>
       <c r="G187" s="27"/>
     </row>
-    <row r="188" spans="1:7">
+    <row r="188" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A188" s="21"/>
       <c r="B188" s="22"/>
       <c r="C188" s="22"/>
@@ -7664,7 +7748,7 @@
       <c r="F188" s="25"/>
       <c r="G188" s="27"/>
     </row>
-    <row r="189" spans="1:7">
+    <row r="189" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A189" s="21"/>
       <c r="B189" s="22"/>
       <c r="C189" s="22"/>
@@ -7673,7 +7757,7 @@
       <c r="F189" s="25"/>
       <c r="G189" s="27"/>
     </row>
-    <row r="190" spans="1:7">
+    <row r="190" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A190" s="21"/>
       <c r="B190" s="22"/>
       <c r="C190" s="22"/>
@@ -7682,7 +7766,7 @@
       <c r="F190" s="25"/>
       <c r="G190" s="27"/>
     </row>
-    <row r="191" spans="1:7">
+    <row r="191" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A191" s="21"/>
       <c r="B191" s="22"/>
       <c r="C191" s="22"/>
@@ -7691,7 +7775,7 @@
       <c r="F191" s="25"/>
       <c r="G191" s="27"/>
     </row>
-    <row r="192" spans="1:7">
+    <row r="192" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A192" s="21"/>
       <c r="B192" s="22"/>
       <c r="C192" s="22"/>
@@ -7700,7 +7784,7 @@
       <c r="F192" s="25"/>
       <c r="G192" s="27"/>
     </row>
-    <row r="193" spans="1:7">
+    <row r="193" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A193" s="21"/>
       <c r="B193" s="22"/>
       <c r="C193" s="22"/>
@@ -7709,7 +7793,7 @@
       <c r="F193" s="25"/>
       <c r="G193" s="27"/>
     </row>
-    <row r="194" spans="1:7">
+    <row r="194" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A194" s="21"/>
       <c r="B194" s="22"/>
       <c r="C194" s="22"/>
@@ -7718,7 +7802,7 @@
       <c r="F194" s="25"/>
       <c r="G194" s="27"/>
     </row>
-    <row r="195" spans="1:7">
+    <row r="195" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A195" s="21"/>
       <c r="B195" s="22"/>
       <c r="C195" s="22"/>
@@ -7727,7 +7811,7 @@
       <c r="F195" s="25"/>
       <c r="G195" s="27"/>
     </row>
-    <row r="196" spans="1:7">
+    <row r="196" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A196" s="21"/>
       <c r="B196" s="22"/>
       <c r="C196" s="22"/>
@@ -7736,7 +7820,7 @@
       <c r="F196" s="30"/>
       <c r="G196" s="31"/>
     </row>
-    <row r="197" spans="1:7">
+    <row r="197" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A197" s="21"/>
       <c r="B197" s="22"/>
       <c r="C197" s="20"/>
@@ -7752,16 +7836,16 @@
     <mergeCell ref="C2:F2"/>
   </mergeCells>
   <conditionalFormatting sqref="E139">
-    <cfRule type="duplicateValues" dxfId="356" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="355" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="354" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="353" priority="75"/>
-    <cfRule type="duplicateValues" dxfId="352" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="351" priority="72"/>
-    <cfRule type="duplicateValues" dxfId="350" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="356" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="355" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="354" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="353" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="352" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="351" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="350" priority="72"/>
     <cfRule type="duplicateValues" dxfId="349" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="348" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="347" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="348" priority="74"/>
+    <cfRule type="duplicateValues" dxfId="347" priority="75"/>
     <cfRule type="duplicateValues" dxfId="346" priority="76"/>
     <cfRule type="duplicateValues" dxfId="345" priority="77"/>
     <cfRule type="duplicateValues" dxfId="344" priority="78"/>
@@ -7769,21 +7853,21 @@
     <cfRule type="duplicateValues" dxfId="342" priority="80"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E196">
-    <cfRule type="duplicateValues" dxfId="341" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="340" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="339" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="338" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="337" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="336" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="335" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="334" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="333" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="332" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="331" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="330" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="329" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="328" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="327" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="341" priority="2"/>
+    <cfRule type="duplicateValues" dxfId="340" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="339" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="338" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="337" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="336" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="335" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="334" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="333" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="332" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="331" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="330" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="329" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="328" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="327" priority="16"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4">
     <cfRule type="duplicateValues" dxfId="326" priority="33"/>
@@ -7798,92 +7882,92 @@
     <cfRule type="duplicateValues" dxfId="323" priority="49"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F139">
-    <cfRule type="duplicateValues" dxfId="322" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="321" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="320" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="319" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="318" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="317" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="316" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="315" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="314" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="322" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="321" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="320" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="319" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="318" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="317" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="316" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="315" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="314" priority="26"/>
     <cfRule type="duplicateValues" dxfId="313" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="312" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="311" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="310" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="309" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="308" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="312" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="311" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="310" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="309" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="308" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F140">
-    <cfRule type="duplicateValues" dxfId="307" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="306" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="305" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="304" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="303" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="302" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="301" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="300" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="299" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="298" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="297" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="296" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="295" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="294" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="293" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="307" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="306" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="305" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="304" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="303" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="302" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="301" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="300" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="299" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="298" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="297" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="296" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="295" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="294" priority="47"/>
+    <cfRule type="duplicateValues" dxfId="293" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F156">
-    <cfRule type="duplicateValues" dxfId="292" priority="101"/>
-    <cfRule type="duplicateValues" dxfId="291" priority="100"/>
-    <cfRule type="duplicateValues" dxfId="290" priority="99"/>
-    <cfRule type="duplicateValues" dxfId="289" priority="97"/>
-    <cfRule type="duplicateValues" dxfId="288" priority="98"/>
-    <cfRule type="duplicateValues" dxfId="287" priority="105"/>
-    <cfRule type="duplicateValues" dxfId="286" priority="110"/>
-    <cfRule type="duplicateValues" dxfId="285" priority="102"/>
-    <cfRule type="duplicateValues" dxfId="284" priority="96"/>
-    <cfRule type="duplicateValues" dxfId="283" priority="103"/>
-    <cfRule type="duplicateValues" dxfId="282" priority="104"/>
-    <cfRule type="duplicateValues" dxfId="281" priority="106"/>
-    <cfRule type="duplicateValues" dxfId="280" priority="107"/>
-    <cfRule type="duplicateValues" dxfId="279" priority="108"/>
-    <cfRule type="duplicateValues" dxfId="278" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="292" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="291" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="290" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="289" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="288" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="287" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="286" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="285" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="284" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="283" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="282" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="281" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="280" priority="108"/>
+    <cfRule type="duplicateValues" dxfId="279" priority="109"/>
+    <cfRule type="duplicateValues" dxfId="278" priority="110"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F157:F194 F79:F138 E139 F141:F155">
-    <cfRule type="duplicateValues" dxfId="277" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="276" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="275" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="274" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="273" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="272" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="271" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="270" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="269" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="268" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="267" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="266" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="265" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="264" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="263" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="277" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="276" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="275" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="274" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="273" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="272" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="271" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="270" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="269" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="268" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="267" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="266" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="265" priority="63"/>
+    <cfRule type="duplicateValues" dxfId="264" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="263" priority="65"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F195 F5:F41 F48:F76">
     <cfRule type="duplicateValues" dxfId="262" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F195">
-    <cfRule type="duplicateValues" dxfId="261" priority="95"/>
-    <cfRule type="duplicateValues" dxfId="260" priority="87"/>
-    <cfRule type="duplicateValues" dxfId="259" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="258" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="257" priority="83"/>
-    <cfRule type="duplicateValues" dxfId="256" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="255" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="254" priority="89"/>
-    <cfRule type="duplicateValues" dxfId="253" priority="90"/>
-    <cfRule type="duplicateValues" dxfId="252" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="261" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="260" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="259" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="258" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="257" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="256" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="255" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="254" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="253" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="252" priority="90"/>
     <cfRule type="duplicateValues" dxfId="251" priority="91"/>
     <cfRule type="duplicateValues" dxfId="250" priority="92"/>
     <cfRule type="duplicateValues" dxfId="249" priority="93"/>
     <cfRule type="duplicateValues" dxfId="248" priority="94"/>
-    <cfRule type="duplicateValues" dxfId="247" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="247" priority="95"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.23" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" fitToWidth="0" orientation="portrait" verticalDpi="0" r:id="rId1"/>
@@ -7892,9 +7976,9 @@
 </file>
 
 <file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0100-000000000000}">
   <dimension ref="A1:H157"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.5703125" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
@@ -7905,15 +7989,15 @@
     <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="64.5" customHeight="1">
-      <c r="B1" s="79"/>
-      <c r="C1" s="79"/>
-      <c r="D1" s="79"/>
-      <c r="E1" s="79"/>
+    <row r="1" spans="1:7" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B1" s="82"/>
+      <c r="C1" s="82"/>
+      <c r="D1" s="82"/>
+      <c r="E1" s="82"/>
       <c r="F1" s="13"/>
       <c r="G1" s="13"/>
     </row>
-    <row r="2" spans="1:7" s="32" customFormat="1" ht="27" customHeight="1">
+    <row r="2" spans="1:7" s="32" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="33"/>
       <c r="C2" s="81" t="s">
         <v>206</v>
@@ -7925,7 +8009,7 @@
         <v>207</v>
       </c>
     </row>
-    <row r="3" spans="1:7" ht="15.75">
+    <row r="3" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A3" s="80" t="s">
         <v>0</v>
       </c>
@@ -7936,7 +8020,7 @@
       <c r="F3" s="80"/>
       <c r="G3" s="80"/>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -7955,7 +8039,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>2024</v>
       </c>
@@ -7974,7 +8058,7 @@
         <v>49</v>
       </c>
     </row>
-    <row r="6" spans="1:7">
+    <row r="6" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>2024</v>
       </c>
@@ -7993,7 +8077,7 @@
         <v>50</v>
       </c>
     </row>
-    <row r="7" spans="1:7">
+    <row r="7" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>2024</v>
       </c>
@@ -8012,7 +8096,7 @@
         <v>51</v>
       </c>
     </row>
-    <row r="8" spans="1:7">
+    <row r="8" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>2024</v>
       </c>
@@ -8031,7 +8115,7 @@
         <v>52</v>
       </c>
     </row>
-    <row r="9" spans="1:7">
+    <row r="9" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>2024</v>
       </c>
@@ -8050,7 +8134,7 @@
         <v>53</v>
       </c>
     </row>
-    <row r="10" spans="1:7">
+    <row r="10" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>2024</v>
       </c>
@@ -8069,7 +8153,7 @@
         <v>54</v>
       </c>
     </row>
-    <row r="11" spans="1:7">
+    <row r="11" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>2024</v>
       </c>
@@ -8088,7 +8172,7 @@
         <v>55</v>
       </c>
     </row>
-    <row r="12" spans="1:7">
+    <row r="12" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>2024</v>
       </c>
@@ -8107,7 +8191,7 @@
         <v>56</v>
       </c>
     </row>
-    <row r="13" spans="1:7">
+    <row r="13" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>2024</v>
       </c>
@@ -8126,7 +8210,7 @@
         <v>57</v>
       </c>
     </row>
-    <row r="14" spans="1:7">
+    <row r="14" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>2024</v>
       </c>
@@ -8145,7 +8229,7 @@
         <v>58</v>
       </c>
     </row>
-    <row r="15" spans="1:7">
+    <row r="15" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>2024</v>
       </c>
@@ -8164,7 +8248,7 @@
         <v>59</v>
       </c>
     </row>
-    <row r="16" spans="1:7">
+    <row r="16" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>2024</v>
       </c>
@@ -8183,7 +8267,7 @@
         <v>60</v>
       </c>
     </row>
-    <row r="17" spans="1:7">
+    <row r="17" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>2024</v>
       </c>
@@ -8202,7 +8286,7 @@
         <v>61</v>
       </c>
     </row>
-    <row r="18" spans="1:7">
+    <row r="18" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>2024</v>
       </c>
@@ -8221,7 +8305,7 @@
         <v>62</v>
       </c>
     </row>
-    <row r="19" spans="1:7">
+    <row r="19" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>2024</v>
       </c>
@@ -8240,7 +8324,7 @@
         <v>63</v>
       </c>
     </row>
-    <row r="20" spans="1:7">
+    <row r="20" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>2024</v>
       </c>
@@ -8259,7 +8343,7 @@
         <v>64</v>
       </c>
     </row>
-    <row r="21" spans="1:7">
+    <row r="21" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>2024</v>
       </c>
@@ -8278,7 +8362,7 @@
         <v>65</v>
       </c>
     </row>
-    <row r="22" spans="1:7">
+    <row r="22" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>2024</v>
       </c>
@@ -8297,7 +8381,7 @@
         <v>66</v>
       </c>
     </row>
-    <row r="23" spans="1:7">
+    <row r="23" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>2024</v>
       </c>
@@ -8316,7 +8400,7 @@
         <v>67</v>
       </c>
     </row>
-    <row r="24" spans="1:7">
+    <row r="24" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>2024</v>
       </c>
@@ -8335,7 +8419,7 @@
         <v>68</v>
       </c>
     </row>
-    <row r="25" spans="1:7">
+    <row r="25" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>2024</v>
       </c>
@@ -8354,7 +8438,7 @@
         <v>69</v>
       </c>
     </row>
-    <row r="26" spans="1:7">
+    <row r="26" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>2024</v>
       </c>
@@ -8373,7 +8457,7 @@
         <v>70</v>
       </c>
     </row>
-    <row r="27" spans="1:7">
+    <row r="27" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>2024</v>
       </c>
@@ -8392,7 +8476,7 @@
         <v>71</v>
       </c>
     </row>
-    <row r="28" spans="1:7">
+    <row r="28" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>2024</v>
       </c>
@@ -8411,7 +8495,7 @@
         <v>72</v>
       </c>
     </row>
-    <row r="29" spans="1:7">
+    <row r="29" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>2024</v>
       </c>
@@ -8430,7 +8514,7 @@
         <v>73</v>
       </c>
     </row>
-    <row r="30" spans="1:7">
+    <row r="30" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>2024</v>
       </c>
@@ -8449,7 +8533,7 @@
         <v>74</v>
       </c>
     </row>
-    <row r="31" spans="1:7">
+    <row r="31" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>2024</v>
       </c>
@@ -8468,7 +8552,7 @@
         <v>75</v>
       </c>
     </row>
-    <row r="32" spans="1:7">
+    <row r="32" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>2024</v>
       </c>
@@ -8487,7 +8571,7 @@
         <v>76</v>
       </c>
     </row>
-    <row r="33" spans="1:8">
+    <row r="33" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>2024</v>
       </c>
@@ -8506,7 +8590,7 @@
         <v>77</v>
       </c>
     </row>
-    <row r="34" spans="1:8">
+    <row r="34" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A34" s="11">
         <v>2024</v>
       </c>
@@ -8525,7 +8609,7 @@
         <v>78</v>
       </c>
     </row>
-    <row r="35" spans="1:8">
+    <row r="35" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>2024</v>
       </c>
@@ -8544,7 +8628,7 @@
         <v>79</v>
       </c>
     </row>
-    <row r="36" spans="1:8">
+    <row r="36" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>2024</v>
       </c>
@@ -8563,7 +8647,7 @@
         <v>80</v>
       </c>
     </row>
-    <row r="37" spans="1:8">
+    <row r="37" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>2024</v>
       </c>
@@ -8582,7 +8666,7 @@
         <v>81</v>
       </c>
     </row>
-    <row r="38" spans="1:8">
+    <row r="38" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>2024</v>
       </c>
@@ -8601,7 +8685,7 @@
         <v>82</v>
       </c>
     </row>
-    <row r="39" spans="1:8" ht="15.75">
+    <row r="39" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A39" s="21"/>
       <c r="B39" s="37">
         <v>35</v>
@@ -8621,7 +8705,7 @@
         <v>213</v>
       </c>
     </row>
-    <row r="40" spans="1:8" ht="15.75">
+    <row r="40" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A40" s="21"/>
       <c r="B40" s="37">
         <v>36</v>
@@ -8631,17 +8715,17 @@
       </c>
       <c r="D40" s="37"/>
       <c r="E40" s="37"/>
-      <c r="F40" s="52">
+      <c r="F40" s="51">
         <v>241641101055</v>
       </c>
-      <c r="G40" s="53" t="s">
+      <c r="G40" s="52" t="s">
         <v>222</v>
       </c>
-      <c r="H40" s="51">
+      <c r="H40" s="50">
         <v>46122</v>
       </c>
     </row>
-    <row r="41" spans="1:8">
+    <row r="41" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A41" s="21"/>
       <c r="B41" s="22"/>
       <c r="C41" s="22"/>
@@ -8650,7 +8734,7 @@
       <c r="F41" s="25"/>
       <c r="G41" s="27"/>
     </row>
-    <row r="42" spans="1:8">
+    <row r="42" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A42" s="21"/>
       <c r="B42" s="22"/>
       <c r="C42" s="22"/>
@@ -8659,7 +8743,7 @@
       <c r="F42" s="25"/>
       <c r="G42" s="27"/>
     </row>
-    <row r="43" spans="1:8">
+    <row r="43" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A43" s="21"/>
       <c r="B43" s="22"/>
       <c r="C43" s="22"/>
@@ -8668,7 +8752,7 @@
       <c r="F43" s="25"/>
       <c r="G43" s="27"/>
     </row>
-    <row r="44" spans="1:8">
+    <row r="44" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A44" s="21"/>
       <c r="B44" s="22"/>
       <c r="C44" s="22"/>
@@ -8677,7 +8761,7 @@
       <c r="F44" s="25"/>
       <c r="G44" s="27"/>
     </row>
-    <row r="45" spans="1:8">
+    <row r="45" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A45" s="21"/>
       <c r="B45" s="22"/>
       <c r="C45" s="22"/>
@@ -8686,7 +8770,7 @@
       <c r="F45" s="25"/>
       <c r="G45" s="27"/>
     </row>
-    <row r="46" spans="1:8">
+    <row r="46" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A46" s="21"/>
       <c r="B46" s="22"/>
       <c r="C46" s="22"/>
@@ -8695,7 +8779,7 @@
       <c r="F46" s="25"/>
       <c r="G46" s="27"/>
     </row>
-    <row r="47" spans="1:8">
+    <row r="47" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A47" s="21"/>
       <c r="B47" s="22"/>
       <c r="C47" s="22"/>
@@ -8704,7 +8788,7 @@
       <c r="F47" s="25"/>
       <c r="G47" s="27"/>
     </row>
-    <row r="48" spans="1:8">
+    <row r="48" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A48" s="21"/>
       <c r="B48" s="22"/>
       <c r="C48" s="22"/>
@@ -8713,7 +8797,7 @@
       <c r="F48" s="25"/>
       <c r="G48" s="27"/>
     </row>
-    <row r="49" spans="1:7">
+    <row r="49" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A49" s="21"/>
       <c r="B49" s="22"/>
       <c r="C49" s="22"/>
@@ -8722,7 +8806,7 @@
       <c r="F49" s="25"/>
       <c r="G49" s="27"/>
     </row>
-    <row r="50" spans="1:7">
+    <row r="50" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A50" s="21"/>
       <c r="B50" s="22"/>
       <c r="C50" s="22"/>
@@ -8731,7 +8815,7 @@
       <c r="F50" s="25"/>
       <c r="G50" s="27"/>
     </row>
-    <row r="51" spans="1:7">
+    <row r="51" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A51" s="21"/>
       <c r="B51" s="22"/>
       <c r="C51" s="22"/>
@@ -8740,7 +8824,7 @@
       <c r="F51" s="25"/>
       <c r="G51" s="27"/>
     </row>
-    <row r="52" spans="1:7">
+    <row r="52" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A52" s="21"/>
       <c r="B52" s="22"/>
       <c r="C52" s="22"/>
@@ -8749,7 +8833,7 @@
       <c r="F52" s="25"/>
       <c r="G52" s="27"/>
     </row>
-    <row r="53" spans="1:7">
+    <row r="53" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A53" s="21"/>
       <c r="B53" s="22"/>
       <c r="C53" s="22"/>
@@ -8758,7 +8842,7 @@
       <c r="F53" s="25"/>
       <c r="G53" s="27"/>
     </row>
-    <row r="54" spans="1:7">
+    <row r="54" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A54" s="21"/>
       <c r="B54" s="22"/>
       <c r="C54" s="22"/>
@@ -8767,7 +8851,7 @@
       <c r="F54" s="25"/>
       <c r="G54" s="27"/>
     </row>
-    <row r="55" spans="1:7">
+    <row r="55" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A55" s="21"/>
       <c r="B55" s="22"/>
       <c r="C55" s="22"/>
@@ -8776,7 +8860,7 @@
       <c r="F55" s="25"/>
       <c r="G55" s="27"/>
     </row>
-    <row r="56" spans="1:7">
+    <row r="56" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A56" s="21"/>
       <c r="B56" s="22"/>
       <c r="C56" s="22"/>
@@ -8785,7 +8869,7 @@
       <c r="F56" s="25"/>
       <c r="G56" s="27"/>
     </row>
-    <row r="57" spans="1:7">
+    <row r="57" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A57" s="21"/>
       <c r="B57" s="22"/>
       <c r="C57" s="22"/>
@@ -8794,7 +8878,7 @@
       <c r="F57" s="25"/>
       <c r="G57" s="27"/>
     </row>
-    <row r="58" spans="1:7">
+    <row r="58" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A58" s="21"/>
       <c r="B58" s="22"/>
       <c r="C58" s="22"/>
@@ -8803,7 +8887,7 @@
       <c r="F58" s="25"/>
       <c r="G58" s="27"/>
     </row>
-    <row r="59" spans="1:7">
+    <row r="59" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A59" s="21"/>
       <c r="B59" s="22"/>
       <c r="C59" s="22"/>
@@ -8812,7 +8896,7 @@
       <c r="F59" s="25"/>
       <c r="G59" s="27"/>
     </row>
-    <row r="60" spans="1:7">
+    <row r="60" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A60" s="21"/>
       <c r="B60" s="22"/>
       <c r="C60" s="22"/>
@@ -8821,7 +8905,7 @@
       <c r="F60" s="25"/>
       <c r="G60" s="27"/>
     </row>
-    <row r="61" spans="1:7">
+    <row r="61" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A61" s="21"/>
       <c r="B61" s="22"/>
       <c r="C61" s="22"/>
@@ -8830,7 +8914,7 @@
       <c r="F61" s="25"/>
       <c r="G61" s="27"/>
     </row>
-    <row r="62" spans="1:7">
+    <row r="62" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A62" s="21"/>
       <c r="B62" s="22"/>
       <c r="C62" s="22"/>
@@ -8839,7 +8923,7 @@
       <c r="F62" s="25"/>
       <c r="G62" s="27"/>
     </row>
-    <row r="63" spans="1:7">
+    <row r="63" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A63" s="21"/>
       <c r="B63" s="22"/>
       <c r="C63" s="22"/>
@@ -8848,7 +8932,7 @@
       <c r="F63" s="25"/>
       <c r="G63" s="27"/>
     </row>
-    <row r="64" spans="1:7">
+    <row r="64" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A64" s="21"/>
       <c r="B64" s="22"/>
       <c r="C64" s="22"/>
@@ -8857,7 +8941,7 @@
       <c r="F64" s="25"/>
       <c r="G64" s="27"/>
     </row>
-    <row r="65" spans="1:7">
+    <row r="65" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A65" s="21"/>
       <c r="B65" s="22"/>
       <c r="C65" s="22"/>
@@ -8866,7 +8950,7 @@
       <c r="F65" s="25"/>
       <c r="G65" s="27"/>
     </row>
-    <row r="66" spans="1:7">
+    <row r="66" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A66" s="21"/>
       <c r="B66" s="22"/>
       <c r="C66" s="22"/>
@@ -8875,7 +8959,7 @@
       <c r="F66" s="25"/>
       <c r="G66" s="27"/>
     </row>
-    <row r="67" spans="1:7">
+    <row r="67" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A67" s="21"/>
       <c r="B67" s="22"/>
       <c r="C67" s="22"/>
@@ -8884,7 +8968,7 @@
       <c r="F67" s="25"/>
       <c r="G67" s="27"/>
     </row>
-    <row r="68" spans="1:7">
+    <row r="68" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A68" s="21"/>
       <c r="B68" s="22"/>
       <c r="C68" s="22"/>
@@ -8893,7 +8977,7 @@
       <c r="F68" s="25"/>
       <c r="G68" s="27"/>
     </row>
-    <row r="69" spans="1:7">
+    <row r="69" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A69" s="21"/>
       <c r="B69" s="22"/>
       <c r="C69" s="22"/>
@@ -8902,7 +8986,7 @@
       <c r="F69" s="25"/>
       <c r="G69" s="27"/>
     </row>
-    <row r="70" spans="1:7">
+    <row r="70" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A70" s="21"/>
       <c r="B70" s="22"/>
       <c r="C70" s="22"/>
@@ -8911,7 +8995,7 @@
       <c r="F70" s="25"/>
       <c r="G70" s="27"/>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="21"/>
       <c r="B71" s="22"/>
       <c r="C71" s="22"/>
@@ -8920,7 +9004,7 @@
       <c r="F71" s="25"/>
       <c r="G71" s="27"/>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="21"/>
       <c r="B72" s="22"/>
       <c r="C72" s="22"/>
@@ -8929,7 +9013,7 @@
       <c r="F72" s="25"/>
       <c r="G72" s="27"/>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="21"/>
       <c r="B73" s="22"/>
       <c r="C73" s="22"/>
@@ -8938,7 +9022,7 @@
       <c r="F73" s="25"/>
       <c r="G73" s="27"/>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="21"/>
       <c r="B74" s="22"/>
       <c r="C74" s="22"/>
@@ -8947,7 +9031,7 @@
       <c r="F74" s="25"/>
       <c r="G74" s="27"/>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="21"/>
       <c r="B75" s="22"/>
       <c r="C75" s="22"/>
@@ -8956,7 +9040,7 @@
       <c r="F75" s="25"/>
       <c r="G75" s="27"/>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="21"/>
       <c r="B76" s="22"/>
       <c r="C76" s="22"/>
@@ -8965,7 +9049,7 @@
       <c r="F76" s="25"/>
       <c r="G76" s="27"/>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="21"/>
       <c r="B77" s="22"/>
       <c r="C77" s="22"/>
@@ -8974,7 +9058,7 @@
       <c r="F77" s="25"/>
       <c r="G77" s="27"/>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="21"/>
       <c r="B78" s="22"/>
       <c r="C78" s="22"/>
@@ -8983,7 +9067,7 @@
       <c r="F78" s="25"/>
       <c r="G78" s="27"/>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="21"/>
       <c r="B79" s="22"/>
       <c r="C79" s="22"/>
@@ -8992,7 +9076,7 @@
       <c r="F79" s="25"/>
       <c r="G79" s="27"/>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="21"/>
       <c r="B80" s="22"/>
       <c r="C80" s="22"/>
@@ -9001,7 +9085,7 @@
       <c r="F80" s="25"/>
       <c r="G80" s="27"/>
     </row>
-    <row r="81" spans="1:7">
+    <row r="81" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A81" s="21"/>
       <c r="B81" s="22"/>
       <c r="C81" s="22"/>
@@ -9010,7 +9094,7 @@
       <c r="F81" s="25"/>
       <c r="G81" s="27"/>
     </row>
-    <row r="82" spans="1:7">
+    <row r="82" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A82" s="21"/>
       <c r="B82" s="22"/>
       <c r="C82" s="22"/>
@@ -9019,7 +9103,7 @@
       <c r="F82" s="25"/>
       <c r="G82" s="27"/>
     </row>
-    <row r="83" spans="1:7">
+    <row r="83" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A83" s="21"/>
       <c r="B83" s="22"/>
       <c r="C83" s="22"/>
@@ -9028,7 +9112,7 @@
       <c r="F83" s="25"/>
       <c r="G83" s="27"/>
     </row>
-    <row r="84" spans="1:7">
+    <row r="84" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A84" s="21"/>
       <c r="B84" s="22"/>
       <c r="C84" s="22"/>
@@ -9037,7 +9121,7 @@
       <c r="F84" s="25"/>
       <c r="G84" s="27"/>
     </row>
-    <row r="85" spans="1:7">
+    <row r="85" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A85" s="21"/>
       <c r="B85" s="22"/>
       <c r="C85" s="22"/>
@@ -9046,7 +9130,7 @@
       <c r="F85" s="25"/>
       <c r="G85" s="27"/>
     </row>
-    <row r="86" spans="1:7">
+    <row r="86" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A86" s="21"/>
       <c r="B86" s="22"/>
       <c r="C86" s="22"/>
@@ -9055,7 +9139,7 @@
       <c r="F86" s="25"/>
       <c r="G86" s="27"/>
     </row>
-    <row r="87" spans="1:7">
+    <row r="87" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A87" s="21"/>
       <c r="B87" s="22"/>
       <c r="C87" s="22"/>
@@ -9064,7 +9148,7 @@
       <c r="F87" s="25"/>
       <c r="G87" s="27"/>
     </row>
-    <row r="88" spans="1:7">
+    <row r="88" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A88" s="21"/>
       <c r="B88" s="22"/>
       <c r="C88" s="22"/>
@@ -9073,7 +9157,7 @@
       <c r="F88" s="25"/>
       <c r="G88" s="27"/>
     </row>
-    <row r="89" spans="1:7">
+    <row r="89" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A89" s="21"/>
       <c r="B89" s="22"/>
       <c r="C89" s="22"/>
@@ -9082,7 +9166,7 @@
       <c r="F89" s="25"/>
       <c r="G89" s="27"/>
     </row>
-    <row r="90" spans="1:7">
+    <row r="90" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A90" s="21"/>
       <c r="B90" s="22"/>
       <c r="C90" s="22"/>
@@ -9091,7 +9175,7 @@
       <c r="F90" s="25"/>
       <c r="G90" s="27"/>
     </row>
-    <row r="91" spans="1:7">
+    <row r="91" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A91" s="21"/>
       <c r="B91" s="22"/>
       <c r="C91" s="22"/>
@@ -9100,7 +9184,7 @@
       <c r="F91" s="25"/>
       <c r="G91" s="27"/>
     </row>
-    <row r="92" spans="1:7">
+    <row r="92" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A92" s="21"/>
       <c r="B92" s="22"/>
       <c r="C92" s="22"/>
@@ -9109,7 +9193,7 @@
       <c r="F92" s="25"/>
       <c r="G92" s="27"/>
     </row>
-    <row r="93" spans="1:7">
+    <row r="93" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A93" s="21"/>
       <c r="B93" s="22"/>
       <c r="C93" s="22"/>
@@ -9118,7 +9202,7 @@
       <c r="F93" s="25"/>
       <c r="G93" s="27"/>
     </row>
-    <row r="94" spans="1:7">
+    <row r="94" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A94" s="21"/>
       <c r="B94" s="22"/>
       <c r="C94" s="22"/>
@@ -9127,7 +9211,7 @@
       <c r="F94" s="25"/>
       <c r="G94" s="27"/>
     </row>
-    <row r="95" spans="1:7">
+    <row r="95" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A95" s="21"/>
       <c r="B95" s="22"/>
       <c r="C95" s="22"/>
@@ -9136,7 +9220,7 @@
       <c r="F95" s="25"/>
       <c r="G95" s="27"/>
     </row>
-    <row r="96" spans="1:7">
+    <row r="96" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A96" s="21"/>
       <c r="B96" s="22"/>
       <c r="C96" s="22"/>
@@ -9145,7 +9229,7 @@
       <c r="F96" s="25"/>
       <c r="G96" s="27"/>
     </row>
-    <row r="97" spans="1:7">
+    <row r="97" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A97" s="21"/>
       <c r="B97" s="22"/>
       <c r="C97" s="22"/>
@@ -9154,7 +9238,7 @@
       <c r="F97" s="25"/>
       <c r="G97" s="27"/>
     </row>
-    <row r="98" spans="1:7">
+    <row r="98" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A98" s="21"/>
       <c r="B98" s="22"/>
       <c r="C98" s="22"/>
@@ -9163,7 +9247,7 @@
       <c r="F98" s="25"/>
       <c r="G98" s="27"/>
     </row>
-    <row r="99" spans="1:7">
+    <row r="99" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A99" s="21"/>
       <c r="B99" s="22"/>
       <c r="C99" s="22"/>
@@ -9172,7 +9256,7 @@
       <c r="F99" s="29"/>
       <c r="G99" s="27"/>
     </row>
-    <row r="100" spans="1:7">
+    <row r="100" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A100" s="21"/>
       <c r="B100" s="22"/>
       <c r="C100" s="22"/>
@@ -9181,7 +9265,7 @@
       <c r="F100" s="25"/>
       <c r="G100" s="27"/>
     </row>
-    <row r="101" spans="1:7">
+    <row r="101" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A101" s="21"/>
       <c r="B101" s="22"/>
       <c r="C101" s="22"/>
@@ -9190,7 +9274,7 @@
       <c r="F101" s="24"/>
       <c r="G101" s="24"/>
     </row>
-    <row r="102" spans="1:7">
+    <row r="102" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A102" s="21"/>
       <c r="B102" s="22"/>
       <c r="C102" s="22"/>
@@ -9199,7 +9283,7 @@
       <c r="F102" s="25"/>
       <c r="G102" s="27"/>
     </row>
-    <row r="103" spans="1:7">
+    <row r="103" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A103" s="21"/>
       <c r="B103" s="22"/>
       <c r="C103" s="22"/>
@@ -9208,7 +9292,7 @@
       <c r="F103" s="25"/>
       <c r="G103" s="27"/>
     </row>
-    <row r="104" spans="1:7">
+    <row r="104" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A104" s="21"/>
       <c r="B104" s="22"/>
       <c r="C104" s="22"/>
@@ -9217,7 +9301,7 @@
       <c r="F104" s="25"/>
       <c r="G104" s="27"/>
     </row>
-    <row r="105" spans="1:7">
+    <row r="105" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A105" s="21"/>
       <c r="B105" s="22"/>
       <c r="C105" s="22"/>
@@ -9226,7 +9310,7 @@
       <c r="F105" s="25"/>
       <c r="G105" s="27"/>
     </row>
-    <row r="106" spans="1:7">
+    <row r="106" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A106" s="21"/>
       <c r="B106" s="22"/>
       <c r="C106" s="22"/>
@@ -9235,7 +9319,7 @@
       <c r="F106" s="25"/>
       <c r="G106" s="27"/>
     </row>
-    <row r="107" spans="1:7">
+    <row r="107" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A107" s="21"/>
       <c r="B107" s="22"/>
       <c r="C107" s="22"/>
@@ -9244,7 +9328,7 @@
       <c r="F107" s="25"/>
       <c r="G107" s="27"/>
     </row>
-    <row r="108" spans="1:7">
+    <row r="108" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A108" s="21"/>
       <c r="B108" s="22"/>
       <c r="C108" s="22"/>
@@ -9253,7 +9337,7 @@
       <c r="F108" s="25"/>
       <c r="G108" s="27"/>
     </row>
-    <row r="109" spans="1:7">
+    <row r="109" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A109" s="21"/>
       <c r="B109" s="22"/>
       <c r="C109" s="22"/>
@@ -9262,7 +9346,7 @@
       <c r="F109" s="25"/>
       <c r="G109" s="27"/>
     </row>
-    <row r="110" spans="1:7">
+    <row r="110" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A110" s="21"/>
       <c r="B110" s="22"/>
       <c r="C110" s="22"/>
@@ -9271,7 +9355,7 @@
       <c r="F110" s="25"/>
       <c r="G110" s="27"/>
     </row>
-    <row r="111" spans="1:7">
+    <row r="111" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A111" s="21"/>
       <c r="B111" s="22"/>
       <c r="C111" s="22"/>
@@ -9280,7 +9364,7 @@
       <c r="F111" s="25"/>
       <c r="G111" s="27"/>
     </row>
-    <row r="112" spans="1:7">
+    <row r="112" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A112" s="21"/>
       <c r="B112" s="22"/>
       <c r="C112" s="22"/>
@@ -9289,7 +9373,7 @@
       <c r="F112" s="25"/>
       <c r="G112" s="27"/>
     </row>
-    <row r="113" spans="1:7">
+    <row r="113" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A113" s="21"/>
       <c r="B113" s="22"/>
       <c r="C113" s="22"/>
@@ -9298,7 +9382,7 @@
       <c r="F113" s="25"/>
       <c r="G113" s="27"/>
     </row>
-    <row r="114" spans="1:7">
+    <row r="114" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A114" s="21"/>
       <c r="B114" s="22"/>
       <c r="C114" s="22"/>
@@ -9307,7 +9391,7 @@
       <c r="F114" s="25"/>
       <c r="G114" s="27"/>
     </row>
-    <row r="115" spans="1:7">
+    <row r="115" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A115" s="21"/>
       <c r="B115" s="22"/>
       <c r="C115" s="22"/>
@@ -9316,7 +9400,7 @@
       <c r="F115" s="25"/>
       <c r="G115" s="27"/>
     </row>
-    <row r="116" spans="1:7">
+    <row r="116" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A116" s="21"/>
       <c r="B116" s="22"/>
       <c r="C116" s="22"/>
@@ -9325,7 +9409,7 @@
       <c r="F116" s="25"/>
       <c r="G116" s="27"/>
     </row>
-    <row r="117" spans="1:7">
+    <row r="117" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A117" s="21"/>
       <c r="B117" s="22"/>
       <c r="C117" s="22"/>
@@ -9334,7 +9418,7 @@
       <c r="F117" s="25"/>
       <c r="G117" s="27"/>
     </row>
-    <row r="118" spans="1:7">
+    <row r="118" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A118" s="21"/>
       <c r="B118" s="22"/>
       <c r="C118" s="22"/>
@@ -9343,7 +9427,7 @@
       <c r="F118" s="25"/>
       <c r="G118" s="27"/>
     </row>
-    <row r="119" spans="1:7">
+    <row r="119" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A119" s="21"/>
       <c r="B119" s="22"/>
       <c r="C119" s="22"/>
@@ -9352,7 +9436,7 @@
       <c r="F119" s="25"/>
       <c r="G119" s="27"/>
     </row>
-    <row r="120" spans="1:7">
+    <row r="120" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A120" s="21"/>
       <c r="B120" s="22"/>
       <c r="C120" s="22"/>
@@ -9361,7 +9445,7 @@
       <c r="F120" s="25"/>
       <c r="G120" s="27"/>
     </row>
-    <row r="121" spans="1:7">
+    <row r="121" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A121" s="21"/>
       <c r="B121" s="22"/>
       <c r="C121" s="22"/>
@@ -9370,7 +9454,7 @@
       <c r="F121" s="25"/>
       <c r="G121" s="27"/>
     </row>
-    <row r="122" spans="1:7">
+    <row r="122" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A122" s="21"/>
       <c r="B122" s="22"/>
       <c r="C122" s="22"/>
@@ -9379,7 +9463,7 @@
       <c r="F122" s="25"/>
       <c r="G122" s="27"/>
     </row>
-    <row r="123" spans="1:7">
+    <row r="123" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A123" s="21"/>
       <c r="B123" s="22"/>
       <c r="C123" s="22"/>
@@ -9388,7 +9472,7 @@
       <c r="F123" s="25"/>
       <c r="G123" s="27"/>
     </row>
-    <row r="124" spans="1:7">
+    <row r="124" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A124" s="21"/>
       <c r="B124" s="22"/>
       <c r="C124" s="22"/>
@@ -9397,7 +9481,7 @@
       <c r="F124" s="25"/>
       <c r="G124" s="27"/>
     </row>
-    <row r="125" spans="1:7">
+    <row r="125" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A125" s="21"/>
       <c r="B125" s="22"/>
       <c r="C125" s="22"/>
@@ -9406,7 +9490,7 @@
       <c r="F125" s="25"/>
       <c r="G125" s="27"/>
     </row>
-    <row r="126" spans="1:7">
+    <row r="126" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A126" s="21"/>
       <c r="B126" s="22"/>
       <c r="C126" s="22"/>
@@ -9415,7 +9499,7 @@
       <c r="F126" s="25"/>
       <c r="G126" s="27"/>
     </row>
-    <row r="127" spans="1:7">
+    <row r="127" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A127" s="21"/>
       <c r="B127" s="22"/>
       <c r="C127" s="22"/>
@@ -9424,7 +9508,7 @@
       <c r="F127" s="25"/>
       <c r="G127" s="27"/>
     </row>
-    <row r="128" spans="1:7">
+    <row r="128" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A128" s="21"/>
       <c r="B128" s="22"/>
       <c r="C128" s="22"/>
@@ -9433,7 +9517,7 @@
       <c r="F128" s="25"/>
       <c r="G128" s="27"/>
     </row>
-    <row r="129" spans="1:7">
+    <row r="129" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A129" s="21"/>
       <c r="B129" s="22"/>
       <c r="C129" s="22"/>
@@ -9442,7 +9526,7 @@
       <c r="F129" s="25"/>
       <c r="G129" s="27"/>
     </row>
-    <row r="130" spans="1:7">
+    <row r="130" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A130" s="21"/>
       <c r="B130" s="22"/>
       <c r="C130" s="22"/>
@@ -9451,7 +9535,7 @@
       <c r="F130" s="25"/>
       <c r="G130" s="27"/>
     </row>
-    <row r="131" spans="1:7">
+    <row r="131" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A131" s="21"/>
       <c r="B131" s="22"/>
       <c r="C131" s="22"/>
@@ -9460,7 +9544,7 @@
       <c r="F131" s="25"/>
       <c r="G131" s="27"/>
     </row>
-    <row r="132" spans="1:7">
+    <row r="132" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A132" s="21"/>
       <c r="B132" s="22"/>
       <c r="C132" s="22"/>
@@ -9469,7 +9553,7 @@
       <c r="F132" s="25"/>
       <c r="G132" s="27"/>
     </row>
-    <row r="133" spans="1:7">
+    <row r="133" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A133" s="21"/>
       <c r="B133" s="22"/>
       <c r="C133" s="22"/>
@@ -9478,7 +9562,7 @@
       <c r="F133" s="25"/>
       <c r="G133" s="27"/>
     </row>
-    <row r="134" spans="1:7">
+    <row r="134" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A134" s="21"/>
       <c r="B134" s="22"/>
       <c r="C134" s="22"/>
@@ -9487,7 +9571,7 @@
       <c r="F134" s="25"/>
       <c r="G134" s="27"/>
     </row>
-    <row r="135" spans="1:7">
+    <row r="135" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A135" s="21"/>
       <c r="B135" s="22"/>
       <c r="C135" s="22"/>
@@ -9496,7 +9580,7 @@
       <c r="F135" s="25"/>
       <c r="G135" s="27"/>
     </row>
-    <row r="136" spans="1:7">
+    <row r="136" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A136" s="21"/>
       <c r="B136" s="22"/>
       <c r="C136" s="22"/>
@@ -9505,7 +9589,7 @@
       <c r="F136" s="25"/>
       <c r="G136" s="27"/>
     </row>
-    <row r="137" spans="1:7">
+    <row r="137" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A137" s="21"/>
       <c r="B137" s="22"/>
       <c r="C137" s="22"/>
@@ -9514,7 +9598,7 @@
       <c r="F137" s="25"/>
       <c r="G137" s="27"/>
     </row>
-    <row r="138" spans="1:7">
+    <row r="138" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A138" s="21"/>
       <c r="B138" s="22"/>
       <c r="C138" s="22"/>
@@ -9523,7 +9607,7 @@
       <c r="F138" s="25"/>
       <c r="G138" s="27"/>
     </row>
-    <row r="139" spans="1:7">
+    <row r="139" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A139" s="21"/>
       <c r="B139" s="22"/>
       <c r="C139" s="22"/>
@@ -9532,7 +9616,7 @@
       <c r="F139" s="25"/>
       <c r="G139" s="27"/>
     </row>
-    <row r="140" spans="1:7">
+    <row r="140" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A140" s="21"/>
       <c r="B140" s="22"/>
       <c r="C140" s="22"/>
@@ -9541,7 +9625,7 @@
       <c r="F140" s="25"/>
       <c r="G140" s="27"/>
     </row>
-    <row r="141" spans="1:7">
+    <row r="141" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A141" s="21"/>
       <c r="B141" s="22"/>
       <c r="C141" s="22"/>
@@ -9550,7 +9634,7 @@
       <c r="F141" s="25"/>
       <c r="G141" s="27"/>
     </row>
-    <row r="142" spans="1:7">
+    <row r="142" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A142" s="21"/>
       <c r="B142" s="22"/>
       <c r="C142" s="22"/>
@@ -9559,7 +9643,7 @@
       <c r="F142" s="25"/>
       <c r="G142" s="27"/>
     </row>
-    <row r="143" spans="1:7">
+    <row r="143" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A143" s="21"/>
       <c r="B143" s="22"/>
       <c r="C143" s="22"/>
@@ -9568,7 +9652,7 @@
       <c r="F143" s="25"/>
       <c r="G143" s="27"/>
     </row>
-    <row r="144" spans="1:7">
+    <row r="144" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A144" s="21"/>
       <c r="B144" s="22"/>
       <c r="C144" s="22"/>
@@ -9577,7 +9661,7 @@
       <c r="F144" s="25"/>
       <c r="G144" s="27"/>
     </row>
-    <row r="145" spans="1:7">
+    <row r="145" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A145" s="21"/>
       <c r="B145" s="22"/>
       <c r="C145" s="22"/>
@@ -9586,7 +9670,7 @@
       <c r="F145" s="25"/>
       <c r="G145" s="27"/>
     </row>
-    <row r="146" spans="1:7">
+    <row r="146" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A146" s="21"/>
       <c r="B146" s="22"/>
       <c r="C146" s="22"/>
@@ -9595,7 +9679,7 @@
       <c r="F146" s="25"/>
       <c r="G146" s="27"/>
     </row>
-    <row r="147" spans="1:7">
+    <row r="147" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A147" s="21"/>
       <c r="B147" s="22"/>
       <c r="C147" s="22"/>
@@ -9604,7 +9688,7 @@
       <c r="F147" s="25"/>
       <c r="G147" s="27"/>
     </row>
-    <row r="148" spans="1:7">
+    <row r="148" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A148" s="21"/>
       <c r="B148" s="22"/>
       <c r="C148" s="22"/>
@@ -9613,7 +9697,7 @@
       <c r="F148" s="25"/>
       <c r="G148" s="27"/>
     </row>
-    <row r="149" spans="1:7">
+    <row r="149" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A149" s="21"/>
       <c r="B149" s="22"/>
       <c r="C149" s="22"/>
@@ -9622,7 +9706,7 @@
       <c r="F149" s="25"/>
       <c r="G149" s="27"/>
     </row>
-    <row r="150" spans="1:7">
+    <row r="150" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A150" s="21"/>
       <c r="B150" s="22"/>
       <c r="C150" s="22"/>
@@ -9631,7 +9715,7 @@
       <c r="F150" s="25"/>
       <c r="G150" s="27"/>
     </row>
-    <row r="151" spans="1:7">
+    <row r="151" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A151" s="21"/>
       <c r="B151" s="22"/>
       <c r="C151" s="22"/>
@@ -9640,7 +9724,7 @@
       <c r="F151" s="25"/>
       <c r="G151" s="27"/>
     </row>
-    <row r="152" spans="1:7">
+    <row r="152" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A152" s="21"/>
       <c r="B152" s="22"/>
       <c r="C152" s="22"/>
@@ -9649,7 +9733,7 @@
       <c r="F152" s="25"/>
       <c r="G152" s="27"/>
     </row>
-    <row r="153" spans="1:7">
+    <row r="153" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A153" s="21"/>
       <c r="B153" s="22"/>
       <c r="C153" s="22"/>
@@ -9658,7 +9742,7 @@
       <c r="F153" s="25"/>
       <c r="G153" s="27"/>
     </row>
-    <row r="154" spans="1:7">
+    <row r="154" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A154" s="21"/>
       <c r="B154" s="22"/>
       <c r="C154" s="22"/>
@@ -9667,7 +9751,7 @@
       <c r="F154" s="25"/>
       <c r="G154" s="27"/>
     </row>
-    <row r="155" spans="1:7">
+    <row r="155" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A155" s="21"/>
       <c r="B155" s="22"/>
       <c r="C155" s="22"/>
@@ -9676,7 +9760,7 @@
       <c r="F155" s="25"/>
       <c r="G155" s="27"/>
     </row>
-    <row r="156" spans="1:7">
+    <row r="156" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A156" s="21"/>
       <c r="B156" s="22"/>
       <c r="C156" s="22"/>
@@ -9685,7 +9769,7 @@
       <c r="F156" s="30"/>
       <c r="G156" s="31"/>
     </row>
-    <row r="157" spans="1:7">
+    <row r="157" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A157" s="21"/>
       <c r="B157" s="22"/>
       <c r="C157" s="20"/>
@@ -9701,16 +9785,16 @@
     <mergeCell ref="C2:F2"/>
   </mergeCells>
   <conditionalFormatting sqref="E99">
-    <cfRule type="duplicateValues" dxfId="246" priority="70"/>
-    <cfRule type="duplicateValues" dxfId="245" priority="71"/>
-    <cfRule type="duplicateValues" dxfId="244" priority="65"/>
-    <cfRule type="duplicateValues" dxfId="243" priority="66"/>
-    <cfRule type="duplicateValues" dxfId="242" priority="67"/>
-    <cfRule type="duplicateValues" dxfId="241" priority="73"/>
-    <cfRule type="duplicateValues" dxfId="240" priority="64"/>
-    <cfRule type="duplicateValues" dxfId="239" priority="69"/>
-    <cfRule type="duplicateValues" dxfId="238" priority="68"/>
-    <cfRule type="duplicateValues" dxfId="237" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="246" priority="64"/>
+    <cfRule type="duplicateValues" dxfId="245" priority="65"/>
+    <cfRule type="duplicateValues" dxfId="244" priority="66"/>
+    <cfRule type="duplicateValues" dxfId="243" priority="67"/>
+    <cfRule type="duplicateValues" dxfId="242" priority="68"/>
+    <cfRule type="duplicateValues" dxfId="241" priority="69"/>
+    <cfRule type="duplicateValues" dxfId="240" priority="70"/>
+    <cfRule type="duplicateValues" dxfId="239" priority="71"/>
+    <cfRule type="duplicateValues" dxfId="238" priority="72"/>
+    <cfRule type="duplicateValues" dxfId="237" priority="73"/>
     <cfRule type="duplicateValues" dxfId="236" priority="74"/>
     <cfRule type="duplicateValues" dxfId="235" priority="75"/>
     <cfRule type="duplicateValues" dxfId="234" priority="76"/>
@@ -9718,21 +9802,21 @@
     <cfRule type="duplicateValues" dxfId="232" priority="78"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="E156">
-    <cfRule type="duplicateValues" dxfId="231" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="230" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="229" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="228" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="227" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="226" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="225" priority="16"/>
-    <cfRule type="duplicateValues" dxfId="224" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="223" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="222" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="221" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="220" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="219" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="218" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="217" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="231" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="230" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="229" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="228" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="227" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="226" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="225" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="224" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="223" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="222" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="221" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="220" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="219" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="218" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="217" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4">
     <cfRule type="duplicateValues" dxfId="216" priority="1"/>
@@ -9741,92 +9825,92 @@
     <cfRule type="duplicateValues" dxfId="215" priority="48"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F99">
-    <cfRule type="duplicateValues" dxfId="214" priority="31"/>
-    <cfRule type="duplicateValues" dxfId="213" priority="32"/>
-    <cfRule type="duplicateValues" dxfId="212" priority="23"/>
-    <cfRule type="duplicateValues" dxfId="211" priority="22"/>
-    <cfRule type="duplicateValues" dxfId="210" priority="21"/>
-    <cfRule type="duplicateValues" dxfId="209" priority="20"/>
-    <cfRule type="duplicateValues" dxfId="208" priority="19"/>
-    <cfRule type="duplicateValues" dxfId="207" priority="18"/>
-    <cfRule type="duplicateValues" dxfId="206" priority="25"/>
-    <cfRule type="duplicateValues" dxfId="205" priority="24"/>
-    <cfRule type="duplicateValues" dxfId="204" priority="26"/>
-    <cfRule type="duplicateValues" dxfId="203" priority="27"/>
-    <cfRule type="duplicateValues" dxfId="202" priority="28"/>
-    <cfRule type="duplicateValues" dxfId="201" priority="29"/>
-    <cfRule type="duplicateValues" dxfId="200" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="214" priority="18"/>
+    <cfRule type="duplicateValues" dxfId="213" priority="19"/>
+    <cfRule type="duplicateValues" dxfId="212" priority="20"/>
+    <cfRule type="duplicateValues" dxfId="211" priority="21"/>
+    <cfRule type="duplicateValues" dxfId="210" priority="22"/>
+    <cfRule type="duplicateValues" dxfId="209" priority="23"/>
+    <cfRule type="duplicateValues" dxfId="208" priority="24"/>
+    <cfRule type="duplicateValues" dxfId="207" priority="25"/>
+    <cfRule type="duplicateValues" dxfId="206" priority="26"/>
+    <cfRule type="duplicateValues" dxfId="205" priority="27"/>
+    <cfRule type="duplicateValues" dxfId="204" priority="28"/>
+    <cfRule type="duplicateValues" dxfId="203" priority="29"/>
+    <cfRule type="duplicateValues" dxfId="202" priority="30"/>
+    <cfRule type="duplicateValues" dxfId="201" priority="31"/>
+    <cfRule type="duplicateValues" dxfId="200" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F100">
-    <cfRule type="duplicateValues" dxfId="199" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="198" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="197" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="196" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="195" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="194" priority="46"/>
-    <cfRule type="duplicateValues" dxfId="193" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="192" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="191" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="190" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="189" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="188" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="187" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="186" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="185" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="199" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="198" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="197" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="196" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="195" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="194" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="193" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="192" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="191" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="190" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="189" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="188" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="187" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="186" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="185" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F116">
-    <cfRule type="duplicateValues" dxfId="184" priority="99"/>
-    <cfRule type="duplicateValues" dxfId="183" priority="98"/>
-    <cfRule type="duplicateValues" dxfId="182" priority="97"/>
-    <cfRule type="duplicateValues" dxfId="181" priority="95"/>
-    <cfRule type="duplicateValues" dxfId="180" priority="96"/>
-    <cfRule type="duplicateValues" dxfId="179" priority="103"/>
-    <cfRule type="duplicateValues" dxfId="178" priority="108"/>
-    <cfRule type="duplicateValues" dxfId="177" priority="94"/>
-    <cfRule type="duplicateValues" dxfId="176" priority="100"/>
-    <cfRule type="duplicateValues" dxfId="175" priority="101"/>
-    <cfRule type="duplicateValues" dxfId="174" priority="102"/>
-    <cfRule type="duplicateValues" dxfId="173" priority="104"/>
-    <cfRule type="duplicateValues" dxfId="172" priority="105"/>
-    <cfRule type="duplicateValues" dxfId="171" priority="106"/>
-    <cfRule type="duplicateValues" dxfId="170" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="184" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="183" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="182" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="181" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="180" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="179" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="178" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="177" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="176" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="175" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="174" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="173" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="172" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="171" priority="107"/>
+    <cfRule type="duplicateValues" dxfId="170" priority="108"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F117:F154 F101:F115 E99 F41:F98">
     <cfRule type="duplicateValues" dxfId="169" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="168" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="167" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="166" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="165" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="164" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="163" priority="61"/>
-    <cfRule type="duplicateValues" dxfId="162" priority="62"/>
-    <cfRule type="duplicateValues" dxfId="161" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="160" priority="63"/>
-    <cfRule type="duplicateValues" dxfId="159" priority="54"/>
-    <cfRule type="duplicateValues" dxfId="158" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="157" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="156" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="155" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="168" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="167" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="166" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="165" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="164" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="163" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="162" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="161" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="160" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="159" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="158" priority="60"/>
+    <cfRule type="duplicateValues" dxfId="157" priority="61"/>
+    <cfRule type="duplicateValues" dxfId="156" priority="62"/>
+    <cfRule type="duplicateValues" dxfId="155" priority="63"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F155 F5:F36">
     <cfRule type="duplicateValues" dxfId="154" priority="2"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F155">
-    <cfRule type="duplicateValues" dxfId="153" priority="93"/>
-    <cfRule type="duplicateValues" dxfId="152" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="151" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="150" priority="83"/>
-    <cfRule type="duplicateValues" dxfId="149" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="148" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="147" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="146" priority="87"/>
-    <cfRule type="duplicateValues" dxfId="145" priority="88"/>
-    <cfRule type="duplicateValues" dxfId="144" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="153" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="152" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="151" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="150" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="149" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="148" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="147" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="146" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="145" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="144" priority="88"/>
     <cfRule type="duplicateValues" dxfId="143" priority="89"/>
     <cfRule type="duplicateValues" dxfId="142" priority="90"/>
     <cfRule type="duplicateValues" dxfId="141" priority="91"/>
     <cfRule type="duplicateValues" dxfId="140" priority="92"/>
-    <cfRule type="duplicateValues" dxfId="139" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="139" priority="93"/>
   </conditionalFormatting>
   <pageMargins left="0.41" right="0.38" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -9835,9 +9919,9 @@
 </file>
 
 <file path=xl/worksheets/sheet3.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0200-000000000000}">
   <dimension ref="A1:G121"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.5703125" customWidth="1"/>
     <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
@@ -9845,16 +9929,17 @@
     <col min="4" max="4" width="20" bestFit="1" customWidth="1"/>
     <col min="5" max="5" width="53.42578125" customWidth="1"/>
     <col min="6" max="6" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="14" max="14" width="9.140625" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:5" ht="64.5" customHeight="1">
-      <c r="A1" s="82"/>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-    </row>
-    <row r="2" spans="1:5" s="32" customFormat="1" ht="27" customHeight="1">
+    <row r="1" spans="1:5" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="78"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+    </row>
+    <row r="2" spans="1:5" s="32" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="33"/>
       <c r="C2" s="81" t="s">
         <v>208</v>
@@ -9864,7 +9949,7 @@
         <v>209</v>
       </c>
     </row>
-    <row r="3" spans="1:5">
+    <row r="3" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A3" s="1" t="s">
         <v>1</v>
       </c>
@@ -9881,7 +9966,7 @@
         <v>5</v>
       </c>
     </row>
-    <row r="4" spans="1:5">
+    <row r="4" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A4" s="5">
         <v>2024</v>
       </c>
@@ -9898,7 +9983,7 @@
         <v>84</v>
       </c>
     </row>
-    <row r="5" spans="1:5">
+    <row r="5" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>2024</v>
       </c>
@@ -9915,7 +10000,7 @@
         <v>85</v>
       </c>
     </row>
-    <row r="6" spans="1:5">
+    <row r="6" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>2024</v>
       </c>
@@ -9932,7 +10017,7 @@
         <v>86</v>
       </c>
     </row>
-    <row r="7" spans="1:5">
+    <row r="7" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>2024</v>
       </c>
@@ -9949,7 +10034,7 @@
         <v>87</v>
       </c>
     </row>
-    <row r="8" spans="1:5">
+    <row r="8" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>2024</v>
       </c>
@@ -9966,7 +10051,7 @@
         <v>88</v>
       </c>
     </row>
-    <row r="9" spans="1:5">
+    <row r="9" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>2024</v>
       </c>
@@ -9983,7 +10068,7 @@
         <v>89</v>
       </c>
     </row>
-    <row r="10" spans="1:5">
+    <row r="10" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>2024</v>
       </c>
@@ -10000,7 +10085,7 @@
         <v>90</v>
       </c>
     </row>
-    <row r="11" spans="1:5">
+    <row r="11" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>2024</v>
       </c>
@@ -10017,7 +10102,7 @@
         <v>91</v>
       </c>
     </row>
-    <row r="12" spans="1:5">
+    <row r="12" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>2024</v>
       </c>
@@ -10034,7 +10119,7 @@
         <v>92</v>
       </c>
     </row>
-    <row r="13" spans="1:5">
+    <row r="13" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>2024</v>
       </c>
@@ -10051,7 +10136,7 @@
         <v>93</v>
       </c>
     </row>
-    <row r="14" spans="1:5">
+    <row r="14" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>2024</v>
       </c>
@@ -10068,7 +10153,7 @@
         <v>94</v>
       </c>
     </row>
-    <row r="15" spans="1:5">
+    <row r="15" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>2024</v>
       </c>
@@ -10085,7 +10170,7 @@
         <v>95</v>
       </c>
     </row>
-    <row r="16" spans="1:5">
+    <row r="16" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>2024</v>
       </c>
@@ -10102,7 +10187,7 @@
         <v>96</v>
       </c>
     </row>
-    <row r="17" spans="1:5">
+    <row r="17" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>2024</v>
       </c>
@@ -10119,7 +10204,7 @@
         <v>97</v>
       </c>
     </row>
-    <row r="18" spans="1:5">
+    <row r="18" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>2024</v>
       </c>
@@ -10136,7 +10221,7 @@
         <v>98</v>
       </c>
     </row>
-    <row r="19" spans="1:5">
+    <row r="19" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>2024</v>
       </c>
@@ -10153,7 +10238,7 @@
         <v>99</v>
       </c>
     </row>
-    <row r="20" spans="1:5">
+    <row r="20" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>2024</v>
       </c>
@@ -10170,7 +10255,7 @@
         <v>100</v>
       </c>
     </row>
-    <row r="21" spans="1:5">
+    <row r="21" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>2024</v>
       </c>
@@ -10187,7 +10272,7 @@
         <v>101</v>
       </c>
     </row>
-    <row r="22" spans="1:5">
+    <row r="22" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>2024</v>
       </c>
@@ -10204,7 +10289,7 @@
         <v>102</v>
       </c>
     </row>
-    <row r="23" spans="1:5">
+    <row r="23" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>2024</v>
       </c>
@@ -10221,7 +10306,7 @@
         <v>103</v>
       </c>
     </row>
-    <row r="24" spans="1:5">
+    <row r="24" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>2024</v>
       </c>
@@ -10238,7 +10323,7 @@
         <v>104</v>
       </c>
     </row>
-    <row r="25" spans="1:5">
+    <row r="25" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>2024</v>
       </c>
@@ -10255,7 +10340,7 @@
         <v>105</v>
       </c>
     </row>
-    <row r="26" spans="1:5">
+    <row r="26" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>2024</v>
       </c>
@@ -10272,7 +10357,7 @@
         <v>106</v>
       </c>
     </row>
-    <row r="27" spans="1:5">
+    <row r="27" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>2024</v>
       </c>
@@ -10289,7 +10374,7 @@
         <v>107</v>
       </c>
     </row>
-    <row r="28" spans="1:5">
+    <row r="28" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>2024</v>
       </c>
@@ -10306,7 +10391,7 @@
         <v>108</v>
       </c>
     </row>
-    <row r="29" spans="1:5">
+    <row r="29" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>2024</v>
       </c>
@@ -10323,7 +10408,7 @@
         <v>109</v>
       </c>
     </row>
-    <row r="30" spans="1:5">
+    <row r="30" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>2024</v>
       </c>
@@ -10340,7 +10425,7 @@
         <v>110</v>
       </c>
     </row>
-    <row r="31" spans="1:5">
+    <row r="31" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>2024</v>
       </c>
@@ -10357,7 +10442,7 @@
         <v>111</v>
       </c>
     </row>
-    <row r="32" spans="1:5">
+    <row r="32" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>2024</v>
       </c>
@@ -10374,7 +10459,7 @@
         <v>112</v>
       </c>
     </row>
-    <row r="33" spans="1:5">
+    <row r="33" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>2024</v>
       </c>
@@ -10391,7 +10476,7 @@
         <v>113</v>
       </c>
     </row>
-    <row r="34" spans="1:5">
+    <row r="34" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>2024</v>
       </c>
@@ -10408,7 +10493,7 @@
         <v>114</v>
       </c>
     </row>
-    <row r="35" spans="1:5">
+    <row r="35" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>2024</v>
       </c>
@@ -10425,7 +10510,7 @@
         <v>115</v>
       </c>
     </row>
-    <row r="36" spans="1:5">
+    <row r="36" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>2024</v>
       </c>
@@ -10442,7 +10527,7 @@
         <v>116</v>
       </c>
     </row>
-    <row r="37" spans="1:5">
+    <row r="37" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>2024</v>
       </c>
@@ -10459,7 +10544,7 @@
         <v>117</v>
       </c>
     </row>
-    <row r="38" spans="1:5">
+    <row r="38" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>2024</v>
       </c>
@@ -10476,7 +10561,7 @@
         <v>118</v>
       </c>
     </row>
-    <row r="39" spans="1:5">
+    <row r="39" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>2024</v>
       </c>
@@ -10493,7 +10578,7 @@
         <v>119</v>
       </c>
     </row>
-    <row r="40" spans="1:5">
+    <row r="40" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>2024</v>
       </c>
@@ -10510,7 +10595,7 @@
         <v>120</v>
       </c>
     </row>
-    <row r="41" spans="1:5">
+    <row r="41" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>2024</v>
       </c>
@@ -10527,7 +10612,7 @@
         <v>121</v>
       </c>
     </row>
-    <row r="42" spans="1:5">
+    <row r="42" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>2024</v>
       </c>
@@ -10544,7 +10629,7 @@
         <v>122</v>
       </c>
     </row>
-    <row r="43" spans="1:5">
+    <row r="43" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>2024</v>
       </c>
@@ -10561,7 +10646,7 @@
         <v>123</v>
       </c>
     </row>
-    <row r="44" spans="1:5">
+    <row r="44" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <v>2024</v>
       </c>
@@ -10578,7 +10663,7 @@
         <v>124</v>
       </c>
     </row>
-    <row r="45" spans="1:5">
+    <row r="45" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <v>2024</v>
       </c>
@@ -10595,7 +10680,7 @@
         <v>125</v>
       </c>
     </row>
-    <row r="46" spans="1:5">
+    <row r="46" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
         <v>2024</v>
       </c>
@@ -10612,7 +10697,7 @@
         <v>126</v>
       </c>
     </row>
-    <row r="47" spans="1:5">
+    <row r="47" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
         <v>2024</v>
       </c>
@@ -10629,7 +10714,7 @@
         <v>127</v>
       </c>
     </row>
-    <row r="48" spans="1:5">
+    <row r="48" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <v>2024</v>
       </c>
@@ -10646,7 +10731,7 @@
         <v>128</v>
       </c>
     </row>
-    <row r="49" spans="1:5">
+    <row r="49" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <v>2024</v>
       </c>
@@ -10663,7 +10748,7 @@
         <v>129</v>
       </c>
     </row>
-    <row r="50" spans="1:5">
+    <row r="50" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
         <v>2024</v>
       </c>
@@ -10680,7 +10765,7 @@
         <v>130</v>
       </c>
     </row>
-    <row r="51" spans="1:5">
+    <row r="51" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <v>2024</v>
       </c>
@@ -10697,7 +10782,7 @@
         <v>131</v>
       </c>
     </row>
-    <row r="52" spans="1:5">
+    <row r="52" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
         <v>2024</v>
       </c>
@@ -10714,7 +10799,7 @@
         <v>132</v>
       </c>
     </row>
-    <row r="53" spans="1:5">
+    <row r="53" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
         <v>2024</v>
       </c>
@@ -10731,7 +10816,7 @@
         <v>133</v>
       </c>
     </row>
-    <row r="54" spans="1:5">
+    <row r="54" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
         <v>2024</v>
       </c>
@@ -10748,7 +10833,7 @@
         <v>134</v>
       </c>
     </row>
-    <row r="55" spans="1:5">
+    <row r="55" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
         <v>2024</v>
       </c>
@@ -10765,7 +10850,7 @@
         <v>135</v>
       </c>
     </row>
-    <row r="56" spans="1:5">
+    <row r="56" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
         <v>2024</v>
       </c>
@@ -10782,7 +10867,7 @@
         <v>136</v>
       </c>
     </row>
-    <row r="57" spans="1:5">
+    <row r="57" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
         <v>2024</v>
       </c>
@@ -10799,7 +10884,7 @@
         <v>137</v>
       </c>
     </row>
-    <row r="58" spans="1:5">
+    <row r="58" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
         <v>2024</v>
       </c>
@@ -10816,7 +10901,7 @@
         <v>138</v>
       </c>
     </row>
-    <row r="59" spans="1:5">
+    <row r="59" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
         <v>2024</v>
       </c>
@@ -10833,7 +10918,7 @@
         <v>139</v>
       </c>
     </row>
-    <row r="60" spans="1:5">
+    <row r="60" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A60" s="5">
         <v>2024</v>
       </c>
@@ -10850,7 +10935,7 @@
         <v>140</v>
       </c>
     </row>
-    <row r="61" spans="1:5">
+    <row r="61" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A61" s="5">
         <v>2024</v>
       </c>
@@ -10867,7 +10952,7 @@
         <v>141</v>
       </c>
     </row>
-    <row r="62" spans="1:5">
+    <row r="62" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A62" s="5">
         <v>2024</v>
       </c>
@@ -10884,7 +10969,7 @@
         <v>142</v>
       </c>
     </row>
-    <row r="63" spans="1:5">
+    <row r="63" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A63" s="5">
         <v>2024</v>
       </c>
@@ -10901,7 +10986,7 @@
         <v>143</v>
       </c>
     </row>
-    <row r="64" spans="1:5">
+    <row r="64" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A64" s="5">
         <v>2024</v>
       </c>
@@ -10918,7 +11003,7 @@
         <v>144</v>
       </c>
     </row>
-    <row r="65" spans="1:7" ht="15.75">
+    <row r="65" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A65" s="5">
         <v>2024</v>
       </c>
@@ -10931,14 +11016,14 @@
       <c r="D65" s="44">
         <v>241641101087</v>
       </c>
-      <c r="E65" s="54" t="s">
+      <c r="E65" s="53" t="s">
         <v>214</v>
       </c>
       <c r="F65" s="40" t="s">
         <v>215</v>
       </c>
     </row>
-    <row r="66" spans="1:7" ht="15.75">
+    <row r="66" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A66" s="5">
         <v>2024</v>
       </c>
@@ -10948,37 +11033,37 @@
       <c r="C66" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="D66" s="56">
+      <c r="D66" s="55">
         <v>241641101107</v>
       </c>
-      <c r="E66" s="55" t="s">
+      <c r="E66" s="54" t="s">
         <v>223</v>
       </c>
-      <c r="F66" s="51">
+      <c r="F66" s="50">
         <v>46122</v>
       </c>
     </row>
-    <row r="67" spans="1:7" ht="15.75">
+    <row r="67" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A67" s="5">
         <v>2024</v>
       </c>
-      <c r="B67" s="57">
+      <c r="B67" s="56">
         <v>64</v>
       </c>
-      <c r="C67" s="57" t="s">
+      <c r="C67" s="56" t="s">
         <v>83</v>
       </c>
-      <c r="D67" s="58">
+      <c r="D67" s="57">
         <v>241641101092</v>
       </c>
-      <c r="E67" s="59" t="s">
+      <c r="E67" s="58" t="s">
         <v>226</v>
       </c>
-      <c r="F67" s="60">
+      <c r="F67" s="59">
         <v>46122</v>
       </c>
     </row>
-    <row r="68" spans="1:7" ht="15.75">
+    <row r="68" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A68" s="5">
         <v>2024</v>
       </c>
@@ -10988,17 +11073,17 @@
       <c r="C68" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="D68" s="61">
+      <c r="D68" s="60">
         <v>241641101116</v>
       </c>
-      <c r="E68" s="62" t="s">
+      <c r="E68" s="61" t="s">
         <v>228</v>
       </c>
       <c r="F68" s="40" t="s">
         <v>229</v>
       </c>
     </row>
-    <row r="69" spans="1:7" ht="15.75">
+    <row r="69" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A69" s="5">
         <v>2024</v>
       </c>
@@ -11008,388 +11093,388 @@
       <c r="C69" s="37" t="s">
         <v>83</v>
       </c>
-      <c r="D69" s="69">
+      <c r="D69" s="68">
         <v>241641101125</v>
       </c>
-      <c r="E69" s="71" t="s">
+      <c r="E69" s="70" t="s">
         <v>239</v>
       </c>
-      <c r="F69" s="72" t="s">
+      <c r="F69" s="71" t="s">
         <v>240</v>
       </c>
-      <c r="G69" s="70"/>
-    </row>
-    <row r="70" spans="1:7" ht="15.75">
+      <c r="G69" s="69"/>
+    </row>
+    <row r="70" spans="1:7" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A70" s="5">
         <v>2024</v>
       </c>
-      <c r="B70" s="75">
+      <c r="B70" s="74">
         <v>67</v>
       </c>
-      <c r="C70" s="76" t="s">
+      <c r="C70" s="75" t="s">
         <v>238</v>
       </c>
-      <c r="D70" s="77">
+      <c r="D70" s="76">
         <v>241641101115</v>
       </c>
-      <c r="E70" s="78" t="s">
+      <c r="E70" s="77" t="s">
         <v>244</v>
       </c>
       <c r="F70" s="40" t="s">
         <v>245</v>
       </c>
     </row>
-    <row r="71" spans="1:7">
+    <row r="71" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A71" s="21"/>
       <c r="B71" s="22"/>
       <c r="C71" s="22"/>
       <c r="D71" s="25"/>
       <c r="E71" s="27"/>
     </row>
-    <row r="72" spans="1:7">
+    <row r="72" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A72" s="21"/>
       <c r="B72" s="22"/>
       <c r="C72" s="22"/>
       <c r="D72" s="25"/>
       <c r="E72" s="27"/>
     </row>
-    <row r="73" spans="1:7">
+    <row r="73" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A73" s="21"/>
       <c r="B73" s="22"/>
       <c r="C73" s="22"/>
       <c r="D73" s="25"/>
       <c r="E73" s="27"/>
     </row>
-    <row r="74" spans="1:7">
+    <row r="74" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A74" s="21"/>
       <c r="B74" s="22"/>
       <c r="C74" s="22"/>
       <c r="D74" s="25"/>
       <c r="E74" s="27"/>
     </row>
-    <row r="75" spans="1:7">
+    <row r="75" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A75" s="21"/>
       <c r="B75" s="22"/>
       <c r="C75" s="22"/>
       <c r="D75" s="25"/>
       <c r="E75" s="27"/>
     </row>
-    <row r="76" spans="1:7">
+    <row r="76" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A76" s="21"/>
       <c r="B76" s="22"/>
       <c r="C76" s="22"/>
       <c r="D76" s="25"/>
       <c r="E76" s="27"/>
     </row>
-    <row r="77" spans="1:7">
+    <row r="77" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A77" s="21"/>
       <c r="B77" s="22"/>
       <c r="C77" s="22"/>
       <c r="D77" s="25"/>
       <c r="E77" s="27"/>
     </row>
-    <row r="78" spans="1:7">
+    <row r="78" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A78" s="21"/>
       <c r="B78" s="22"/>
       <c r="C78" s="22"/>
       <c r="D78" s="25"/>
       <c r="E78" s="27"/>
     </row>
-    <row r="79" spans="1:7">
+    <row r="79" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A79" s="21"/>
       <c r="B79" s="22"/>
       <c r="C79" s="22"/>
       <c r="D79" s="25"/>
       <c r="E79" s="27"/>
     </row>
-    <row r="80" spans="1:7">
+    <row r="80" spans="1:7" x14ac:dyDescent="0.25">
       <c r="A80" s="21"/>
       <c r="B80" s="22"/>
       <c r="C80" s="22"/>
       <c r="D80" s="25"/>
       <c r="E80" s="27"/>
     </row>
-    <row r="81" spans="1:5">
+    <row r="81" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A81" s="21"/>
       <c r="B81" s="22"/>
       <c r="C81" s="22"/>
       <c r="D81" s="25"/>
       <c r="E81" s="27"/>
     </row>
-    <row r="82" spans="1:5">
+    <row r="82" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A82" s="21"/>
       <c r="B82" s="22"/>
       <c r="C82" s="22"/>
       <c r="D82" s="25"/>
       <c r="E82" s="27"/>
     </row>
-    <row r="83" spans="1:5">
+    <row r="83" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A83" s="21"/>
       <c r="B83" s="22"/>
       <c r="C83" s="22"/>
       <c r="D83" s="25"/>
       <c r="E83" s="27"/>
     </row>
-    <row r="84" spans="1:5">
+    <row r="84" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A84" s="21"/>
       <c r="B84" s="22"/>
       <c r="C84" s="22"/>
       <c r="D84" s="25"/>
       <c r="E84" s="27"/>
     </row>
-    <row r="85" spans="1:5">
+    <row r="85" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A85" s="21"/>
       <c r="B85" s="22"/>
       <c r="C85" s="22"/>
       <c r="D85" s="25"/>
       <c r="E85" s="27"/>
     </row>
-    <row r="86" spans="1:5">
+    <row r="86" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A86" s="21"/>
       <c r="B86" s="22"/>
       <c r="C86" s="22"/>
       <c r="D86" s="25"/>
       <c r="E86" s="27"/>
     </row>
-    <row r="87" spans="1:5">
+    <row r="87" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A87" s="21"/>
       <c r="B87" s="22"/>
       <c r="C87" s="22"/>
       <c r="D87" s="25"/>
       <c r="E87" s="27"/>
     </row>
-    <row r="88" spans="1:5">
+    <row r="88" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A88" s="21"/>
       <c r="B88" s="22"/>
       <c r="C88" s="22"/>
       <c r="D88" s="25"/>
       <c r="E88" s="27"/>
     </row>
-    <row r="89" spans="1:5">
+    <row r="89" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A89" s="21"/>
       <c r="B89" s="22"/>
       <c r="C89" s="22"/>
       <c r="D89" s="25"/>
       <c r="E89" s="27"/>
     </row>
-    <row r="90" spans="1:5">
+    <row r="90" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A90" s="21"/>
       <c r="B90" s="22"/>
       <c r="C90" s="22"/>
       <c r="D90" s="25"/>
       <c r="E90" s="27"/>
     </row>
-    <row r="91" spans="1:5">
+    <row r="91" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A91" s="21"/>
       <c r="B91" s="22"/>
       <c r="C91" s="22"/>
       <c r="D91" s="25"/>
       <c r="E91" s="27"/>
     </row>
-    <row r="92" spans="1:5">
+    <row r="92" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A92" s="21"/>
       <c r="B92" s="22"/>
       <c r="C92" s="22"/>
       <c r="D92" s="25"/>
       <c r="E92" s="27"/>
     </row>
-    <row r="93" spans="1:5">
+    <row r="93" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A93" s="21"/>
       <c r="B93" s="22"/>
       <c r="C93" s="22"/>
       <c r="D93" s="25"/>
       <c r="E93" s="27"/>
     </row>
-    <row r="94" spans="1:5">
+    <row r="94" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A94" s="21"/>
       <c r="B94" s="22"/>
       <c r="C94" s="22"/>
       <c r="D94" s="25"/>
       <c r="E94" s="27"/>
     </row>
-    <row r="95" spans="1:5">
+    <row r="95" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A95" s="21"/>
       <c r="B95" s="22"/>
       <c r="C95" s="22"/>
       <c r="D95" s="25"/>
       <c r="E95" s="27"/>
     </row>
-    <row r="96" spans="1:5">
+    <row r="96" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A96" s="21"/>
       <c r="B96" s="22"/>
       <c r="C96" s="22"/>
       <c r="D96" s="25"/>
       <c r="E96" s="27"/>
     </row>
-    <row r="97" spans="1:5">
+    <row r="97" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A97" s="21"/>
       <c r="B97" s="22"/>
       <c r="C97" s="22"/>
       <c r="D97" s="25"/>
       <c r="E97" s="27"/>
     </row>
-    <row r="98" spans="1:5">
+    <row r="98" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A98" s="21"/>
       <c r="B98" s="22"/>
       <c r="C98" s="22"/>
       <c r="D98" s="25"/>
       <c r="E98" s="27"/>
     </row>
-    <row r="99" spans="1:5">
+    <row r="99" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A99" s="21"/>
       <c r="B99" s="22"/>
       <c r="C99" s="22"/>
       <c r="D99" s="25"/>
       <c r="E99" s="27"/>
     </row>
-    <row r="100" spans="1:5">
+    <row r="100" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A100" s="21"/>
       <c r="B100" s="22"/>
       <c r="C100" s="22"/>
       <c r="D100" s="25"/>
       <c r="E100" s="27"/>
     </row>
-    <row r="101" spans="1:5">
+    <row r="101" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A101" s="21"/>
       <c r="B101" s="22"/>
       <c r="C101" s="22"/>
       <c r="D101" s="25"/>
       <c r="E101" s="27"/>
     </row>
-    <row r="102" spans="1:5">
+    <row r="102" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A102" s="21"/>
       <c r="B102" s="22"/>
       <c r="C102" s="22"/>
       <c r="D102" s="25"/>
       <c r="E102" s="27"/>
     </row>
-    <row r="103" spans="1:5">
+    <row r="103" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A103" s="21"/>
       <c r="B103" s="22"/>
       <c r="C103" s="22"/>
       <c r="D103" s="25"/>
       <c r="E103" s="27"/>
     </row>
-    <row r="104" spans="1:5">
+    <row r="104" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A104" s="21"/>
       <c r="B104" s="22"/>
       <c r="C104" s="22"/>
       <c r="D104" s="25"/>
       <c r="E104" s="27"/>
     </row>
-    <row r="105" spans="1:5">
+    <row r="105" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A105" s="21"/>
       <c r="B105" s="22"/>
       <c r="C105" s="22"/>
       <c r="D105" s="25"/>
       <c r="E105" s="27"/>
     </row>
-    <row r="106" spans="1:5">
+    <row r="106" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A106" s="21"/>
       <c r="B106" s="22"/>
       <c r="C106" s="22"/>
       <c r="D106" s="25"/>
       <c r="E106" s="27"/>
     </row>
-    <row r="107" spans="1:5">
+    <row r="107" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A107" s="21"/>
       <c r="B107" s="22"/>
       <c r="C107" s="22"/>
       <c r="D107" s="25"/>
       <c r="E107" s="27"/>
     </row>
-    <row r="108" spans="1:5">
+    <row r="108" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A108" s="21"/>
       <c r="B108" s="22"/>
       <c r="C108" s="22"/>
       <c r="D108" s="25"/>
       <c r="E108" s="27"/>
     </row>
-    <row r="109" spans="1:5">
+    <row r="109" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A109" s="21"/>
       <c r="B109" s="22"/>
       <c r="C109" s="22"/>
       <c r="D109" s="25"/>
       <c r="E109" s="27"/>
     </row>
-    <row r="110" spans="1:5">
+    <row r="110" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A110" s="21"/>
       <c r="B110" s="22"/>
       <c r="C110" s="22"/>
       <c r="D110" s="25"/>
       <c r="E110" s="27"/>
     </row>
-    <row r="111" spans="1:5">
+    <row r="111" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A111" s="21"/>
       <c r="B111" s="22"/>
       <c r="C111" s="22"/>
       <c r="D111" s="25"/>
       <c r="E111" s="27"/>
     </row>
-    <row r="112" spans="1:5">
+    <row r="112" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A112" s="21"/>
       <c r="B112" s="22"/>
       <c r="C112" s="22"/>
       <c r="D112" s="25"/>
       <c r="E112" s="27"/>
     </row>
-    <row r="113" spans="1:5">
+    <row r="113" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A113" s="21"/>
       <c r="B113" s="22"/>
       <c r="C113" s="22"/>
       <c r="D113" s="25"/>
       <c r="E113" s="27"/>
     </row>
-    <row r="114" spans="1:5">
+    <row r="114" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A114" s="21"/>
       <c r="B114" s="22"/>
       <c r="C114" s="22"/>
       <c r="D114" s="25"/>
       <c r="E114" s="27"/>
     </row>
-    <row r="115" spans="1:5">
+    <row r="115" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A115" s="21"/>
       <c r="B115" s="22"/>
       <c r="C115" s="22"/>
       <c r="D115" s="25"/>
       <c r="E115" s="27"/>
     </row>
-    <row r="116" spans="1:5">
+    <row r="116" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A116" s="21"/>
       <c r="B116" s="22"/>
       <c r="C116" s="22"/>
       <c r="D116" s="25"/>
       <c r="E116" s="27"/>
     </row>
-    <row r="117" spans="1:5">
+    <row r="117" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A117" s="21"/>
       <c r="B117" s="22"/>
       <c r="C117" s="22"/>
       <c r="D117" s="25"/>
       <c r="E117" s="27"/>
     </row>
-    <row r="118" spans="1:5">
+    <row r="118" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A118" s="21"/>
       <c r="B118" s="22"/>
       <c r="C118" s="22"/>
       <c r="D118" s="25"/>
       <c r="E118" s="27"/>
     </row>
-    <row r="119" spans="1:5">
+    <row r="119" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A119" s="21"/>
       <c r="B119" s="22"/>
       <c r="C119" s="22"/>
       <c r="D119" s="25"/>
       <c r="E119" s="27"/>
     </row>
-    <row r="120" spans="1:5">
+    <row r="120" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A120" s="21"/>
       <c r="B120" s="22"/>
       <c r="C120" s="22"/>
       <c r="D120" s="30"/>
       <c r="E120" s="31"/>
     </row>
-    <row r="121" spans="1:5">
+    <row r="121" spans="1:5" x14ac:dyDescent="0.25">
       <c r="A121" s="21"/>
       <c r="B121" s="22"/>
       <c r="C121" s="20"/>
@@ -11422,38 +11507,38 @@
     <cfRule type="duplicateValues" dxfId="123" priority="32"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D64">
-    <cfRule type="duplicateValues" dxfId="122" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="121" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="120" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="119" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="118" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="117" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="116" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="115" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="114" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="113" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="112" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="111" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="110" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="109" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="108" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="122" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="121" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="120" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="119" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="118" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="117" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="116" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="115" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="114" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="113" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="112" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="111" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="110" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="109" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="108" priority="47"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D80">
-    <cfRule type="duplicateValues" dxfId="107" priority="100"/>
-    <cfRule type="duplicateValues" dxfId="106" priority="101"/>
-    <cfRule type="duplicateValues" dxfId="105" priority="102"/>
-    <cfRule type="duplicateValues" dxfId="104" priority="103"/>
-    <cfRule type="duplicateValues" dxfId="103" priority="104"/>
-    <cfRule type="duplicateValues" dxfId="102" priority="105"/>
-    <cfRule type="duplicateValues" dxfId="101" priority="106"/>
-    <cfRule type="duplicateValues" dxfId="100" priority="107"/>
-    <cfRule type="duplicateValues" dxfId="99" priority="98"/>
-    <cfRule type="duplicateValues" dxfId="98" priority="93"/>
-    <cfRule type="duplicateValues" dxfId="97" priority="94"/>
-    <cfRule type="duplicateValues" dxfId="96" priority="95"/>
-    <cfRule type="duplicateValues" dxfId="95" priority="96"/>
-    <cfRule type="duplicateValues" dxfId="94" priority="97"/>
-    <cfRule type="duplicateValues" dxfId="93" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="107" priority="93"/>
+    <cfRule type="duplicateValues" dxfId="106" priority="94"/>
+    <cfRule type="duplicateValues" dxfId="105" priority="95"/>
+    <cfRule type="duplicateValues" dxfId="104" priority="96"/>
+    <cfRule type="duplicateValues" dxfId="103" priority="97"/>
+    <cfRule type="duplicateValues" dxfId="102" priority="98"/>
+    <cfRule type="duplicateValues" dxfId="101" priority="99"/>
+    <cfRule type="duplicateValues" dxfId="100" priority="100"/>
+    <cfRule type="duplicateValues" dxfId="99" priority="101"/>
+    <cfRule type="duplicateValues" dxfId="98" priority="102"/>
+    <cfRule type="duplicateValues" dxfId="97" priority="103"/>
+    <cfRule type="duplicateValues" dxfId="96" priority="104"/>
+    <cfRule type="duplicateValues" dxfId="95" priority="105"/>
+    <cfRule type="duplicateValues" dxfId="94" priority="106"/>
+    <cfRule type="duplicateValues" dxfId="93" priority="107"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D81:D118 D4:D62 D71:D79">
     <cfRule type="duplicateValues" dxfId="92" priority="48"/>
@@ -11462,33 +11547,33 @@
     <cfRule type="duplicateValues" dxfId="89" priority="51"/>
     <cfRule type="duplicateValues" dxfId="88" priority="52"/>
     <cfRule type="duplicateValues" dxfId="87" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="86" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="85" priority="56"/>
-    <cfRule type="duplicateValues" dxfId="84" priority="57"/>
-    <cfRule type="duplicateValues" dxfId="83" priority="58"/>
-    <cfRule type="duplicateValues" dxfId="82" priority="59"/>
-    <cfRule type="duplicateValues" dxfId="81" priority="60"/>
-    <cfRule type="duplicateValues" dxfId="80" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="86" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="85" priority="55"/>
+    <cfRule type="duplicateValues" dxfId="84" priority="56"/>
+    <cfRule type="duplicateValues" dxfId="83" priority="57"/>
+    <cfRule type="duplicateValues" dxfId="82" priority="58"/>
+    <cfRule type="duplicateValues" dxfId="81" priority="59"/>
+    <cfRule type="duplicateValues" dxfId="80" priority="60"/>
     <cfRule type="duplicateValues" dxfId="79" priority="61"/>
     <cfRule type="duplicateValues" dxfId="78" priority="62"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="D119">
     <cfRule type="duplicateValues" dxfId="77" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="76" priority="84"/>
-    <cfRule type="duplicateValues" dxfId="75" priority="85"/>
-    <cfRule type="duplicateValues" dxfId="74" priority="86"/>
-    <cfRule type="duplicateValues" dxfId="73" priority="87"/>
-    <cfRule type="duplicateValues" dxfId="72" priority="88"/>
-    <cfRule type="duplicateValues" dxfId="71" priority="90"/>
-    <cfRule type="duplicateValues" dxfId="70" priority="91"/>
-    <cfRule type="duplicateValues" dxfId="69" priority="92"/>
-    <cfRule type="duplicateValues" dxfId="68" priority="78"/>
-    <cfRule type="duplicateValues" dxfId="67" priority="79"/>
-    <cfRule type="duplicateValues" dxfId="66" priority="80"/>
-    <cfRule type="duplicateValues" dxfId="65" priority="81"/>
-    <cfRule type="duplicateValues" dxfId="64" priority="82"/>
-    <cfRule type="duplicateValues" dxfId="63" priority="83"/>
-    <cfRule type="duplicateValues" dxfId="62" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="76" priority="78"/>
+    <cfRule type="duplicateValues" dxfId="75" priority="79"/>
+    <cfRule type="duplicateValues" dxfId="74" priority="80"/>
+    <cfRule type="duplicateValues" dxfId="73" priority="81"/>
+    <cfRule type="duplicateValues" dxfId="72" priority="82"/>
+    <cfRule type="duplicateValues" dxfId="71" priority="83"/>
+    <cfRule type="duplicateValues" dxfId="70" priority="84"/>
+    <cfRule type="duplicateValues" dxfId="69" priority="85"/>
+    <cfRule type="duplicateValues" dxfId="68" priority="86"/>
+    <cfRule type="duplicateValues" dxfId="67" priority="87"/>
+    <cfRule type="duplicateValues" dxfId="66" priority="88"/>
+    <cfRule type="duplicateValues" dxfId="65" priority="89"/>
+    <cfRule type="duplicateValues" dxfId="64" priority="90"/>
+    <cfRule type="duplicateValues" dxfId="63" priority="91"/>
+    <cfRule type="duplicateValues" dxfId="62" priority="92"/>
   </conditionalFormatting>
   <pageMargins left="0.28000000000000003" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
@@ -11497,9 +11582,9 @@
 </file>
 
 <file path=xl/worksheets/sheet4.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships">
-  <dimension ref="A1:H70"/>
-  <sheetFormatPr defaultRowHeight="15"/>
+<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0300-000000000000}">
+  <dimension ref="A1:S70"/>
+  <sheetFormatPr defaultRowHeight="15" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="6.5703125" hidden="1" customWidth="1"/>
     <col min="2" max="2" width="7.140625" bestFit="1" customWidth="1"/>
@@ -11507,19 +11592,19 @@
     <col min="4" max="5" width="0" hidden="1" customWidth="1"/>
     <col min="6" max="6" width="20" bestFit="1" customWidth="1"/>
     <col min="7" max="7" width="51.85546875" customWidth="1"/>
-    <col min="8" max="8" width="10.42578125" bestFit="1" customWidth="1"/>
+    <col min="8" max="8" width="10.42578125" style="64" bestFit="1" customWidth="1"/>
   </cols>
   <sheetData>
-    <row r="1" spans="1:7" ht="64.5" customHeight="1">
-      <c r="A1" s="82"/>
-      <c r="B1" s="82"/>
-      <c r="C1" s="82"/>
-      <c r="D1" s="82"/>
-      <c r="E1" s="82"/>
-      <c r="F1" s="82"/>
-      <c r="G1" s="82"/>
-    </row>
-    <row r="2" spans="1:7" s="32" customFormat="1" ht="27" customHeight="1">
+    <row r="1" spans="1:8" ht="64.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A1" s="78"/>
+      <c r="B1" s="78"/>
+      <c r="C1" s="78"/>
+      <c r="D1" s="78"/>
+      <c r="E1" s="78"/>
+      <c r="F1" s="78"/>
+      <c r="G1" s="78"/>
+    </row>
+    <row r="2" spans="1:8" s="32" customFormat="1" ht="27" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B2" s="33"/>
       <c r="C2" s="81" t="s">
         <v>210</v>
@@ -11530,9 +11615,10 @@
       <c r="G2" s="34" t="s">
         <v>211</v>
       </c>
-    </row>
-    <row r="3" spans="1:7" ht="15.75">
-      <c r="A3" s="83" t="s">
+      <c r="H2" s="91"/>
+    </row>
+    <row r="3" spans="1:8" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="A3" s="79" t="s">
         <v>203</v>
       </c>
       <c r="B3" s="80"/>
@@ -11542,7 +11628,7 @@
       <c r="F3" s="80"/>
       <c r="G3" s="80"/>
     </row>
-    <row r="4" spans="1:7">
+    <row r="4" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A4" s="1" t="s">
         <v>1</v>
       </c>
@@ -11557,11 +11643,11 @@
       <c r="F4" s="3" t="s">
         <v>4</v>
       </c>
-      <c r="G4" s="2" t="s">
+      <c r="G4" s="84" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="5" spans="1:7">
+    <row r="5" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A5" s="5">
         <v>2024</v>
       </c>
@@ -11576,11 +11662,12 @@
       <c r="F5" s="7">
         <v>241641101156</v>
       </c>
-      <c r="G5" s="14" t="s">
+      <c r="G5" s="85" t="s">
         <v>146</v>
       </c>
-    </row>
-    <row r="6" spans="1:7">
+      <c r="H5" s="95"/>
+    </row>
+    <row r="6" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A6" s="5">
         <v>2024</v>
       </c>
@@ -11595,11 +11682,12 @@
       <c r="F6" s="7">
         <v>241641101157</v>
       </c>
-      <c r="G6" s="14" t="s">
+      <c r="G6" s="85" t="s">
         <v>147</v>
       </c>
-    </row>
-    <row r="7" spans="1:7">
+      <c r="H6" s="95"/>
+    </row>
+    <row r="7" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A7" s="5">
         <v>2024</v>
       </c>
@@ -11614,11 +11702,12 @@
       <c r="F7" s="7">
         <v>241641101158</v>
       </c>
-      <c r="G7" s="14" t="s">
+      <c r="G7" s="85" t="s">
         <v>148</v>
       </c>
-    </row>
-    <row r="8" spans="1:7">
+      <c r="H7" s="95"/>
+    </row>
+    <row r="8" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A8" s="5">
         <v>2024</v>
       </c>
@@ -11633,11 +11722,12 @@
       <c r="F8" s="7">
         <v>241641101160</v>
       </c>
-      <c r="G8" s="14" t="s">
+      <c r="G8" s="85" t="s">
         <v>149</v>
       </c>
-    </row>
-    <row r="9" spans="1:7">
+      <c r="H8" s="95"/>
+    </row>
+    <row r="9" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A9" s="5">
         <v>2024</v>
       </c>
@@ -11652,11 +11742,12 @@
       <c r="F9" s="7">
         <v>241641101161</v>
       </c>
-      <c r="G9" s="14" t="s">
+      <c r="G9" s="85" t="s">
         <v>150</v>
       </c>
-    </row>
-    <row r="10" spans="1:7">
+      <c r="H9" s="95"/>
+    </row>
+    <row r="10" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A10" s="5">
         <v>2024</v>
       </c>
@@ -11671,11 +11762,12 @@
       <c r="F10" s="7">
         <v>241641101162</v>
       </c>
-      <c r="G10" s="14" t="s">
+      <c r="G10" s="85" t="s">
         <v>151</v>
       </c>
-    </row>
-    <row r="11" spans="1:7">
+      <c r="H10" s="92"/>
+    </row>
+    <row r="11" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A11" s="5">
         <v>2024</v>
       </c>
@@ -11690,11 +11782,12 @@
       <c r="F11" s="7">
         <v>241641101163</v>
       </c>
-      <c r="G11" s="14" t="s">
+      <c r="G11" s="85" t="s">
         <v>152</v>
       </c>
-    </row>
-    <row r="12" spans="1:7">
+      <c r="H11" s="95"/>
+    </row>
+    <row r="12" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A12" s="5">
         <v>2024</v>
       </c>
@@ -11709,11 +11802,12 @@
       <c r="F12" s="7">
         <v>241641101165</v>
       </c>
-      <c r="G12" s="14" t="s">
+      <c r="G12" s="85" t="s">
         <v>153</v>
       </c>
-    </row>
-    <row r="13" spans="1:7">
+      <c r="H12" s="92"/>
+    </row>
+    <row r="13" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A13" s="5">
         <v>2024</v>
       </c>
@@ -11728,11 +11822,12 @@
       <c r="F13" s="7">
         <v>241641101166</v>
       </c>
-      <c r="G13" s="14" t="s">
+      <c r="G13" s="85" t="s">
         <v>154</v>
       </c>
-    </row>
-    <row r="14" spans="1:7">
+      <c r="H13" s="92"/>
+    </row>
+    <row r="14" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A14" s="5">
         <v>2024</v>
       </c>
@@ -11747,11 +11842,12 @@
       <c r="F14" s="7">
         <v>241641101167</v>
       </c>
-      <c r="G14" s="14" t="s">
+      <c r="G14" s="85" t="s">
         <v>155</v>
       </c>
-    </row>
-    <row r="15" spans="1:7">
+      <c r="H14" s="92"/>
+    </row>
+    <row r="15" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A15" s="5">
         <v>2024</v>
       </c>
@@ -11766,11 +11862,12 @@
       <c r="F15" s="7">
         <v>241641101168</v>
       </c>
-      <c r="G15" s="14" t="s">
+      <c r="G15" s="85" t="s">
         <v>156</v>
       </c>
-    </row>
-    <row r="16" spans="1:7">
+      <c r="H15" s="96"/>
+    </row>
+    <row r="16" spans="1:8" x14ac:dyDescent="0.25">
       <c r="A16" s="5">
         <v>2024</v>
       </c>
@@ -11785,11 +11882,12 @@
       <c r="F16" s="7">
         <v>241641101170</v>
       </c>
-      <c r="G16" s="14" t="s">
+      <c r="G16" s="85" t="s">
         <v>157</v>
       </c>
-    </row>
-    <row r="17" spans="1:7">
+      <c r="H16" s="95"/>
+    </row>
+    <row r="17" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A17" s="5">
         <v>2024</v>
       </c>
@@ -11804,11 +11902,12 @@
       <c r="F17" s="7">
         <v>241641101173</v>
       </c>
-      <c r="G17" s="14" t="s">
+      <c r="G17" s="85" t="s">
         <v>158</v>
       </c>
-    </row>
-    <row r="18" spans="1:7">
+      <c r="H17" s="96"/>
+    </row>
+    <row r="18" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A18" s="5">
         <v>2024</v>
       </c>
@@ -11823,11 +11922,12 @@
       <c r="F18" s="7">
         <v>241641101174</v>
       </c>
-      <c r="G18" s="14" t="s">
+      <c r="G18" s="85" t="s">
         <v>159</v>
       </c>
-    </row>
-    <row r="19" spans="1:7">
+      <c r="H18" s="96"/>
+    </row>
+    <row r="19" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A19" s="5">
         <v>2024</v>
       </c>
@@ -11842,11 +11942,12 @@
       <c r="F19" s="7">
         <v>241641101175</v>
       </c>
-      <c r="G19" s="14" t="s">
+      <c r="G19" s="85" t="s">
         <v>160</v>
       </c>
-    </row>
-    <row r="20" spans="1:7">
+      <c r="H19" s="92"/>
+    </row>
+    <row r="20" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A20" s="5">
         <v>2024</v>
       </c>
@@ -11861,11 +11962,12 @@
       <c r="F20" s="7">
         <v>241641101177</v>
       </c>
-      <c r="G20" s="14" t="s">
+      <c r="G20" s="85" t="s">
         <v>161</v>
       </c>
-    </row>
-    <row r="21" spans="1:7">
+      <c r="H20" s="92"/>
+    </row>
+    <row r="21" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A21" s="5">
         <v>2024</v>
       </c>
@@ -11880,11 +11982,12 @@
       <c r="F21" s="7">
         <v>241641101178</v>
       </c>
-      <c r="G21" s="14" t="s">
+      <c r="G21" s="85" t="s">
         <v>162</v>
       </c>
-    </row>
-    <row r="22" spans="1:7">
+      <c r="H21" s="93"/>
+    </row>
+    <row r="22" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A22" s="5">
         <v>2024</v>
       </c>
@@ -11899,11 +12002,12 @@
       <c r="F22" s="7">
         <v>241641101179</v>
       </c>
-      <c r="G22" s="14" t="s">
+      <c r="G22" s="85" t="s">
         <v>163</v>
       </c>
-    </row>
-    <row r="23" spans="1:7">
+      <c r="H22" s="95"/>
+    </row>
+    <row r="23" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A23" s="5">
         <v>2024</v>
       </c>
@@ -11918,11 +12022,12 @@
       <c r="F23" s="7">
         <v>241641101180</v>
       </c>
-      <c r="G23" s="14" t="s">
+      <c r="G23" s="85" t="s">
         <v>164</v>
       </c>
-    </row>
-    <row r="24" spans="1:7">
+      <c r="H23" s="94"/>
+    </row>
+    <row r="24" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A24" s="5">
         <v>2024</v>
       </c>
@@ -11937,11 +12042,13 @@
       <c r="F24" s="7">
         <v>241641101181</v>
       </c>
-      <c r="G24" s="14" t="s">
+      <c r="G24" s="85" t="s">
         <v>165</v>
       </c>
-    </row>
-    <row r="25" spans="1:7">
+      <c r="H24" s="96"/>
+      <c r="L24" s="96"/>
+    </row>
+    <row r="25" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A25" s="5">
         <v>2024</v>
       </c>
@@ -11956,11 +12063,12 @@
       <c r="F25" s="7">
         <v>241641101182</v>
       </c>
-      <c r="G25" s="14" t="s">
+      <c r="G25" s="85" t="s">
         <v>166</v>
       </c>
-    </row>
-    <row r="26" spans="1:7">
+      <c r="H25" s="94"/>
+    </row>
+    <row r="26" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A26" s="5">
         <v>2024</v>
       </c>
@@ -11975,11 +12083,12 @@
       <c r="F26" s="7">
         <v>241641101183</v>
       </c>
-      <c r="G26" s="14" t="s">
+      <c r="G26" s="85" t="s">
         <v>167</v>
       </c>
-    </row>
-    <row r="27" spans="1:7">
+      <c r="H26" s="95"/>
+    </row>
+    <row r="27" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A27" s="5">
         <v>2024</v>
       </c>
@@ -11994,11 +12103,12 @@
       <c r="F27" s="7">
         <v>241641101184</v>
       </c>
-      <c r="G27" s="14" t="s">
+      <c r="G27" s="85" t="s">
         <v>168</v>
       </c>
-    </row>
-    <row r="28" spans="1:7">
+      <c r="H27" s="95"/>
+    </row>
+    <row r="28" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A28" s="5">
         <v>2024</v>
       </c>
@@ -12013,11 +12123,12 @@
       <c r="F28" s="7">
         <v>241641101186</v>
       </c>
-      <c r="G28" s="14" t="s">
+      <c r="G28" s="85" t="s">
         <v>169</v>
       </c>
-    </row>
-    <row r="29" spans="1:7">
+      <c r="H28" s="95"/>
+    </row>
+    <row r="29" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A29" s="5">
         <v>2024</v>
       </c>
@@ -12032,11 +12143,12 @@
       <c r="F29" s="7">
         <v>241641101187</v>
       </c>
-      <c r="G29" s="14" t="s">
+      <c r="G29" s="85" t="s">
         <v>170</v>
       </c>
-    </row>
-    <row r="30" spans="1:7">
+      <c r="H29" s="96"/>
+    </row>
+    <row r="30" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A30" s="5">
         <v>2024</v>
       </c>
@@ -12051,11 +12163,12 @@
       <c r="F30" s="7">
         <v>241641101188</v>
       </c>
-      <c r="G30" s="14" t="s">
+      <c r="G30" s="85" t="s">
         <v>171</v>
       </c>
-    </row>
-    <row r="31" spans="1:7">
+      <c r="H30" s="95"/>
+    </row>
+    <row r="31" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A31" s="5">
         <v>2024</v>
       </c>
@@ -12070,11 +12183,12 @@
       <c r="F31" s="7">
         <v>241641101189</v>
       </c>
-      <c r="G31" s="14" t="s">
+      <c r="G31" s="85" t="s">
         <v>172</v>
       </c>
-    </row>
-    <row r="32" spans="1:7">
+      <c r="H31" s="92"/>
+    </row>
+    <row r="32" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A32" s="5">
         <v>2024</v>
       </c>
@@ -12089,11 +12203,12 @@
       <c r="F32" s="7">
         <v>241641101190</v>
       </c>
-      <c r="G32" s="14" t="s">
+      <c r="G32" s="85" t="s">
         <v>173</v>
       </c>
-    </row>
-    <row r="33" spans="1:7">
+      <c r="H32" s="96"/>
+    </row>
+    <row r="33" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A33" s="5">
         <v>2024</v>
       </c>
@@ -12108,11 +12223,12 @@
       <c r="F33" s="7">
         <v>241641101191</v>
       </c>
-      <c r="G33" s="14" t="s">
+      <c r="G33" s="85" t="s">
         <v>174</v>
       </c>
-    </row>
-    <row r="34" spans="1:7">
+      <c r="H33" s="92"/>
+    </row>
+    <row r="34" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A34" s="5">
         <v>2024</v>
       </c>
@@ -12127,11 +12243,12 @@
       <c r="F34" s="7">
         <v>241641101195</v>
       </c>
-      <c r="G34" s="14" t="s">
+      <c r="G34" s="85" t="s">
         <v>175</v>
       </c>
-    </row>
-    <row r="35" spans="1:7">
+      <c r="H34" s="95"/>
+    </row>
+    <row r="35" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A35" s="5">
         <v>2024</v>
       </c>
@@ -12146,11 +12263,12 @@
       <c r="F35" s="7">
         <v>241641101196</v>
       </c>
-      <c r="G35" s="14" t="s">
+      <c r="G35" s="85" t="s">
         <v>176</v>
       </c>
-    </row>
-    <row r="36" spans="1:7">
+      <c r="H35" s="92"/>
+    </row>
+    <row r="36" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A36" s="5">
         <v>2024</v>
       </c>
@@ -12165,11 +12283,12 @@
       <c r="F36" s="7">
         <v>241641101197</v>
       </c>
-      <c r="G36" s="14" t="s">
+      <c r="G36" s="85" t="s">
         <v>177</v>
       </c>
-    </row>
-    <row r="37" spans="1:7">
+      <c r="H36" s="92"/>
+    </row>
+    <row r="37" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A37" s="5">
         <v>2024</v>
       </c>
@@ -12184,11 +12303,12 @@
       <c r="F37" s="7">
         <v>241641101200</v>
       </c>
-      <c r="G37" s="14" t="s">
+      <c r="G37" s="85" t="s">
         <v>178</v>
       </c>
-    </row>
-    <row r="38" spans="1:7">
+      <c r="H37" s="94"/>
+    </row>
+    <row r="38" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A38" s="5">
         <v>2024</v>
       </c>
@@ -12203,11 +12323,12 @@
       <c r="F38" s="7">
         <v>241641101201</v>
       </c>
-      <c r="G38" s="14" t="s">
+      <c r="G38" s="85" t="s">
         <v>179</v>
       </c>
-    </row>
-    <row r="39" spans="1:7">
+      <c r="H38" s="92"/>
+    </row>
+    <row r="39" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A39" s="5">
         <v>2024</v>
       </c>
@@ -12222,11 +12343,13 @@
       <c r="F39" s="7">
         <v>241641101202</v>
       </c>
-      <c r="G39" s="14" t="s">
+      <c r="G39" s="85" t="s">
         <v>180</v>
       </c>
-    </row>
-    <row r="40" spans="1:7">
+      <c r="H39" s="97"/>
+      <c r="I39" s="97"/>
+    </row>
+    <row r="40" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A40" s="5">
         <v>2024</v>
       </c>
@@ -12241,11 +12364,12 @@
       <c r="F40" s="7">
         <v>241641101203</v>
       </c>
-      <c r="G40" s="14" t="s">
+      <c r="G40" s="85" t="s">
         <v>181</v>
       </c>
-    </row>
-    <row r="41" spans="1:7">
+      <c r="H40" s="94"/>
+    </row>
+    <row r="41" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A41" s="5">
         <v>2024</v>
       </c>
@@ -12260,11 +12384,12 @@
       <c r="F41" s="7">
         <v>241641101204</v>
       </c>
-      <c r="G41" s="14" t="s">
+      <c r="G41" s="85" t="s">
         <v>182</v>
       </c>
-    </row>
-    <row r="42" spans="1:7">
+      <c r="H41" s="95"/>
+    </row>
+    <row r="42" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A42" s="5">
         <v>2024</v>
       </c>
@@ -12279,11 +12404,12 @@
       <c r="F42" s="7">
         <v>241641101206</v>
       </c>
-      <c r="G42" s="14" t="s">
+      <c r="G42" s="85" t="s">
         <v>183</v>
       </c>
-    </row>
-    <row r="43" spans="1:7">
+      <c r="H42" s="94"/>
+    </row>
+    <row r="43" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A43" s="5">
         <v>2024</v>
       </c>
@@ -12298,11 +12424,12 @@
       <c r="F43" s="7">
         <v>241641101207</v>
       </c>
-      <c r="G43" s="14" t="s">
+      <c r="G43" s="85" t="s">
         <v>184</v>
       </c>
-    </row>
-    <row r="44" spans="1:7">
+      <c r="H43" s="96"/>
+    </row>
+    <row r="44" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A44" s="5">
         <v>2024</v>
       </c>
@@ -12317,11 +12444,17 @@
       <c r="F44" s="7">
         <v>241641101208</v>
       </c>
-      <c r="G44" s="14" t="s">
+      <c r="G44" s="85" t="s">
         <v>185</v>
       </c>
-    </row>
-    <row r="45" spans="1:7">
+      <c r="H44" s="97"/>
+      <c r="I44" s="97"/>
+      <c r="J44" s="98"/>
+      <c r="K44" s="98"/>
+      <c r="L44" s="98"/>
+      <c r="M44" s="98"/>
+    </row>
+    <row r="45" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A45" s="5">
         <v>2024</v>
       </c>
@@ -12336,11 +12469,12 @@
       <c r="F45" s="7">
         <v>241641101210</v>
       </c>
-      <c r="G45" s="14" t="s">
+      <c r="G45" s="85" t="s">
         <v>186</v>
       </c>
-    </row>
-    <row r="46" spans="1:7">
+      <c r="H45" s="95"/>
+    </row>
+    <row r="46" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A46" s="5">
         <v>2024</v>
       </c>
@@ -12355,11 +12489,12 @@
       <c r="F46" s="7">
         <v>241641101211</v>
       </c>
-      <c r="G46" s="14" t="s">
+      <c r="G46" s="85" t="s">
         <v>187</v>
       </c>
-    </row>
-    <row r="47" spans="1:7">
+      <c r="H46" s="96"/>
+    </row>
+    <row r="47" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A47" s="5">
         <v>2024</v>
       </c>
@@ -12374,11 +12509,12 @@
       <c r="F47" s="7">
         <v>241641101212</v>
       </c>
-      <c r="G47" s="14" t="s">
+      <c r="G47" s="85" t="s">
         <v>188</v>
       </c>
-    </row>
-    <row r="48" spans="1:7">
+      <c r="H47" s="94"/>
+    </row>
+    <row r="48" spans="1:13" x14ac:dyDescent="0.25">
       <c r="A48" s="5">
         <v>2024</v>
       </c>
@@ -12393,11 +12529,12 @@
       <c r="F48" s="7">
         <v>241641101214</v>
       </c>
-      <c r="G48" s="14" t="s">
+      <c r="G48" s="85" t="s">
         <v>189</v>
       </c>
-    </row>
-    <row r="49" spans="1:8">
+      <c r="H48" s="95"/>
+    </row>
+    <row r="49" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A49" s="5">
         <v>2024</v>
       </c>
@@ -12412,11 +12549,12 @@
       <c r="F49" s="7">
         <v>241641101215</v>
       </c>
-      <c r="G49" s="14" t="s">
+      <c r="G49" s="85" t="s">
         <v>190</v>
       </c>
-    </row>
-    <row r="50" spans="1:8">
+      <c r="H49" s="95"/>
+    </row>
+    <row r="50" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A50" s="5">
         <v>2024</v>
       </c>
@@ -12431,11 +12569,12 @@
       <c r="F50" s="7">
         <v>241641101216</v>
       </c>
-      <c r="G50" s="14" t="s">
+      <c r="G50" s="85" t="s">
         <v>191</v>
       </c>
-    </row>
-    <row r="51" spans="1:8">
+      <c r="H50" s="95"/>
+    </row>
+    <row r="51" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A51" s="5">
         <v>2024</v>
       </c>
@@ -12450,11 +12589,12 @@
       <c r="F51" s="7">
         <v>241641101217</v>
       </c>
-      <c r="G51" s="14" t="s">
+      <c r="G51" s="85" t="s">
         <v>192</v>
       </c>
-    </row>
-    <row r="52" spans="1:8">
+      <c r="H51" s="95"/>
+    </row>
+    <row r="52" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A52" s="5">
         <v>2024</v>
       </c>
@@ -12469,11 +12609,12 @@
       <c r="F52" s="7">
         <v>241641101219</v>
       </c>
-      <c r="G52" s="14" t="s">
+      <c r="G52" s="85" t="s">
         <v>193</v>
       </c>
-    </row>
-    <row r="53" spans="1:8">
+      <c r="H52" s="92"/>
+    </row>
+    <row r="53" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A53" s="5">
         <v>2024</v>
       </c>
@@ -12488,11 +12629,12 @@
       <c r="F53" s="7">
         <v>241641101220</v>
       </c>
-      <c r="G53" s="14" t="s">
+      <c r="G53" s="85" t="s">
         <v>194</v>
       </c>
-    </row>
-    <row r="54" spans="1:8">
+      <c r="H53" s="95"/>
+    </row>
+    <row r="54" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A54" s="5">
         <v>2024</v>
       </c>
@@ -12507,11 +12649,12 @@
       <c r="F54" s="7">
         <v>241641101221</v>
       </c>
-      <c r="G54" s="14" t="s">
+      <c r="G54" s="85" t="s">
         <v>195</v>
       </c>
-    </row>
-    <row r="55" spans="1:8">
+      <c r="H54" s="95"/>
+    </row>
+    <row r="55" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A55" s="5">
         <v>2024</v>
       </c>
@@ -12526,11 +12669,12 @@
       <c r="F55" s="7">
         <v>241641101222</v>
       </c>
-      <c r="G55" s="14" t="s">
+      <c r="G55" s="85" t="s">
         <v>196</v>
       </c>
-    </row>
-    <row r="56" spans="1:8">
+      <c r="H55" s="94"/>
+    </row>
+    <row r="56" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A56" s="5">
         <v>2024</v>
       </c>
@@ -12545,11 +12689,12 @@
       <c r="F56" s="7">
         <v>241641101223</v>
       </c>
-      <c r="G56" s="14" t="s">
+      <c r="G56" s="85" t="s">
         <v>197</v>
       </c>
-    </row>
-    <row r="57" spans="1:8">
+      <c r="H56" s="95"/>
+    </row>
+    <row r="57" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A57" s="5">
         <v>2024</v>
       </c>
@@ -12564,11 +12709,12 @@
       <c r="F57" s="7">
         <v>241641101224</v>
       </c>
-      <c r="G57" s="14" t="s">
+      <c r="G57" s="85" t="s">
         <v>198</v>
       </c>
-    </row>
-    <row r="58" spans="1:8">
+      <c r="H57" s="94"/>
+    </row>
+    <row r="58" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A58" s="5">
         <v>2024</v>
       </c>
@@ -12583,11 +12729,12 @@
       <c r="F58" s="7">
         <v>241641101185</v>
       </c>
-      <c r="G58" s="14" t="s">
+      <c r="G58" s="85" t="s">
         <v>199</v>
       </c>
-    </row>
-    <row r="59" spans="1:8">
+      <c r="H58" s="94"/>
+    </row>
+    <row r="59" spans="1:12" x14ac:dyDescent="0.25">
       <c r="A59" s="5">
         <v>2024</v>
       </c>
@@ -12604,11 +12751,12 @@
       <c r="F59" s="48">
         <v>241641102781</v>
       </c>
-      <c r="G59" s="49" t="s">
+      <c r="G59" s="86" t="s">
         <v>202</v>
       </c>
-    </row>
-    <row r="60" spans="1:8" ht="15.75">
+      <c r="H59" s="95"/>
+    </row>
+    <row r="60" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="A60" s="45"/>
       <c r="B60" s="37">
         <v>56</v>
@@ -12621,14 +12769,15 @@
       <c r="F60" s="44">
         <v>241641101192</v>
       </c>
-      <c r="G60" s="42" t="s">
+      <c r="G60" s="87" t="s">
         <v>219</v>
       </c>
       <c r="H60" s="40" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="61" spans="1:8" ht="15.75">
+      <c r="I60" s="96"/>
+    </row>
+    <row r="61" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B61" s="37">
         <v>57</v>
       </c>
@@ -12640,14 +12789,15 @@
       <c r="F61" s="44">
         <v>241641101209</v>
       </c>
-      <c r="G61" s="42" t="s">
+      <c r="G61" s="87" t="s">
         <v>220</v>
       </c>
       <c r="H61" s="40" t="s">
         <v>218</v>
       </c>
-    </row>
-    <row r="62" spans="1:8">
+      <c r="I61" s="95"/>
+    </row>
+    <row r="62" spans="1:12" x14ac:dyDescent="0.25">
       <c r="B62" s="37">
         <v>58</v>
       </c>
@@ -12656,76 +12806,84 @@
       </c>
       <c r="D62" s="40"/>
       <c r="E62" s="40"/>
-      <c r="F62" s="63">
+      <c r="F62" s="62">
         <v>241641101205</v>
       </c>
-      <c r="G62" s="50" t="s">
+      <c r="G62" s="88" t="s">
         <v>221</v>
       </c>
-      <c r="H62" s="51">
+      <c r="H62" s="50">
         <v>46121</v>
       </c>
-    </row>
-    <row r="63" spans="1:8" ht="18.75" customHeight="1">
+      <c r="I62" s="96"/>
+    </row>
+    <row r="63" spans="1:12" ht="18.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="B63" s="37">
         <v>59</v>
       </c>
       <c r="C63" s="37" t="s">
         <v>200</v>
       </c>
-      <c r="D63" s="64" t="s">
+      <c r="D63" s="63" t="s">
         <v>224</v>
       </c>
-      <c r="E63" s="65"/>
-      <c r="F63" s="56">
+      <c r="E63" s="64"/>
+      <c r="F63" s="55">
         <v>241641101176</v>
       </c>
-      <c r="G63" s="53" t="s">
+      <c r="G63" s="89" t="s">
         <v>224</v>
       </c>
-      <c r="H63" s="51">
+      <c r="H63" s="50">
         <v>46122</v>
       </c>
-    </row>
-    <row r="64" spans="1:8" ht="15.75">
+      <c r="I63" s="95"/>
+    </row>
+    <row r="64" spans="1:12" ht="15.75" x14ac:dyDescent="0.25">
       <c r="B64" s="37">
         <v>60</v>
       </c>
       <c r="C64" s="37" t="s">
         <v>200</v>
       </c>
-      <c r="D64" s="65"/>
-      <c r="E64" s="65"/>
-      <c r="F64" s="56">
+      <c r="D64" s="64"/>
+      <c r="E64" s="64"/>
+      <c r="F64" s="55">
         <v>241641101193</v>
       </c>
-      <c r="G64" s="53" t="s">
+      <c r="G64" s="89" t="s">
         <v>225</v>
       </c>
-      <c r="H64" s="51">
+      <c r="H64" s="50">
         <v>46122</v>
       </c>
-    </row>
-    <row r="65" spans="2:8">
+      <c r="I64" s="97"/>
+      <c r="J64" s="97"/>
+      <c r="K64" s="98"/>
+      <c r="L64" s="98"/>
+    </row>
+    <row r="65" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B65" s="37">
         <v>61</v>
       </c>
       <c r="C65" s="37" t="s">
         <v>200</v>
       </c>
-      <c r="D65" s="65"/>
-      <c r="E65" s="65"/>
-      <c r="F65" s="63">
+      <c r="D65" s="64"/>
+      <c r="E65" s="64"/>
+      <c r="F65" s="62">
         <v>241641101164</v>
       </c>
-      <c r="G65" s="50" t="s">
+      <c r="G65" s="88" t="s">
         <v>227</v>
       </c>
-      <c r="H65" s="51">
+      <c r="H65" s="50">
         <v>46125</v>
       </c>
-    </row>
-    <row r="66" spans="2:8">
+      <c r="I65" s="94"/>
+      <c r="S65" s="83"/>
+    </row>
+    <row r="66" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B66" s="37">
         <v>62</v>
       </c>
@@ -12734,17 +12892,19 @@
       </c>
       <c r="D66" s="40"/>
       <c r="E66" s="40"/>
-      <c r="F66" s="67">
+      <c r="F66" s="66">
         <v>241641101172</v>
       </c>
-      <c r="G66" s="66" t="s">
+      <c r="G66" s="90" t="s">
         <v>230</v>
       </c>
       <c r="H66" s="40" t="s">
         <v>231</v>
       </c>
-    </row>
-    <row r="67" spans="2:8">
+      <c r="I66" s="94"/>
+      <c r="L66" s="13"/>
+    </row>
+    <row r="67" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B67" s="37">
         <v>63</v>
       </c>
@@ -12753,17 +12913,18 @@
       </c>
       <c r="D67" s="40"/>
       <c r="E67" s="40"/>
-      <c r="F67" s="63">
+      <c r="F67" s="62">
         <v>241641101199</v>
       </c>
-      <c r="G67" s="50" t="s">
+      <c r="G67" s="88" t="s">
         <v>232</v>
       </c>
       <c r="H67" s="40" t="s">
         <v>233</v>
       </c>
-    </row>
-    <row r="68" spans="2:8">
+      <c r="I67" s="96"/>
+    </row>
+    <row r="68" spans="2:19" x14ac:dyDescent="0.25">
       <c r="B68" s="37">
         <v>64</v>
       </c>
@@ -12772,61 +12933,67 @@
       </c>
       <c r="D68" s="40"/>
       <c r="E68" s="40"/>
-      <c r="F68" s="63">
+      <c r="F68" s="62">
         <v>241641101198</v>
       </c>
-      <c r="G68" s="50" t="s">
+      <c r="G68" s="88" t="s">
         <v>236</v>
       </c>
       <c r="H68" s="40" t="s">
         <v>237</v>
       </c>
-    </row>
-    <row r="69" spans="2:8" ht="15.75">
-      <c r="B69" s="73">
+      <c r="I68" s="94"/>
+    </row>
+    <row r="69" spans="2:19" ht="15.75" x14ac:dyDescent="0.25">
+      <c r="B69" s="72">
         <v>65</v>
       </c>
       <c r="C69" s="37" t="s">
         <v>200</v>
       </c>
-      <c r="D69" s="74" t="s">
+      <c r="D69" s="73" t="s">
         <v>238</v>
       </c>
-      <c r="E69" s="72">
+      <c r="E69" s="71">
         <v>241641101125</v>
       </c>
       <c r="F69" s="44">
         <v>241641101194</v>
       </c>
-      <c r="G69" s="42" t="s">
+      <c r="G69" s="87" t="s">
         <v>243</v>
       </c>
       <c r="H69" s="40" t="s">
         <v>242</v>
       </c>
-    </row>
-    <row r="70" spans="2:8" ht="16.5" customHeight="1">
-      <c r="B70" s="74">
+      <c r="I69" s="97"/>
+      <c r="J69" s="97"/>
+      <c r="K69" s="98"/>
+      <c r="L69" s="98"/>
+    </row>
+    <row r="70" spans="2:19" ht="16.5" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="B70" s="73">
         <v>66</v>
       </c>
-      <c r="C70" s="74" t="s">
+      <c r="C70" s="73" t="s">
         <v>200</v>
       </c>
-      <c r="D70" s="72">
+      <c r="D70" s="71">
         <v>241641101213</v>
       </c>
-      <c r="E70" s="50" t="s">
+      <c r="E70" s="49" t="s">
         <v>246</v>
       </c>
-      <c r="F70" s="63">
+      <c r="F70" s="62">
         <v>241641101213</v>
       </c>
-      <c r="G70" s="50" t="s">
+      <c r="G70" s="88" t="s">
         <v>246</v>
       </c>
       <c r="H70" s="40" t="s">
         <v>247</v>
       </c>
+      <c r="I70" s="96"/>
     </row>
   </sheetData>
   <mergeCells count="3">
@@ -12835,34 +13002,34 @@
     <mergeCell ref="C2:F2"/>
   </mergeCells>
   <conditionalFormatting sqref="E59">
-    <cfRule type="duplicateValues" dxfId="61" priority="8"/>
-    <cfRule type="duplicateValues" dxfId="60" priority="17"/>
-    <cfRule type="duplicateValues" dxfId="59" priority="3"/>
-    <cfRule type="duplicateValues" dxfId="58" priority="4"/>
-    <cfRule type="duplicateValues" dxfId="57" priority="5"/>
-    <cfRule type="duplicateValues" dxfId="56" priority="6"/>
-    <cfRule type="duplicateValues" dxfId="55" priority="7"/>
-    <cfRule type="duplicateValues" dxfId="54" priority="15"/>
-    <cfRule type="duplicateValues" dxfId="53" priority="9"/>
-    <cfRule type="duplicateValues" dxfId="52" priority="10"/>
-    <cfRule type="duplicateValues" dxfId="51" priority="11"/>
-    <cfRule type="duplicateValues" dxfId="50" priority="12"/>
-    <cfRule type="duplicateValues" dxfId="49" priority="13"/>
-    <cfRule type="duplicateValues" dxfId="48" priority="14"/>
-    <cfRule type="duplicateValues" dxfId="47" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="61" priority="3"/>
+    <cfRule type="duplicateValues" dxfId="60" priority="4"/>
+    <cfRule type="duplicateValues" dxfId="59" priority="5"/>
+    <cfRule type="duplicateValues" dxfId="58" priority="6"/>
+    <cfRule type="duplicateValues" dxfId="57" priority="7"/>
+    <cfRule type="duplicateValues" dxfId="56" priority="8"/>
+    <cfRule type="duplicateValues" dxfId="55" priority="9"/>
+    <cfRule type="duplicateValues" dxfId="54" priority="10"/>
+    <cfRule type="duplicateValues" dxfId="53" priority="11"/>
+    <cfRule type="duplicateValues" dxfId="52" priority="12"/>
+    <cfRule type="duplicateValues" dxfId="51" priority="13"/>
+    <cfRule type="duplicateValues" dxfId="50" priority="14"/>
+    <cfRule type="duplicateValues" dxfId="49" priority="15"/>
+    <cfRule type="duplicateValues" dxfId="48" priority="16"/>
+    <cfRule type="duplicateValues" dxfId="47" priority="17"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F4">
     <cfRule type="duplicateValues" dxfId="46" priority="1"/>
   </conditionalFormatting>
   <conditionalFormatting sqref="F19">
-    <cfRule type="duplicateValues" dxfId="45" priority="55"/>
-    <cfRule type="duplicateValues" dxfId="44" priority="48"/>
-    <cfRule type="duplicateValues" dxfId="43" priority="49"/>
-    <cfRule type="duplicateValues" dxfId="42" priority="50"/>
-    <cfRule type="duplicateValues" dxfId="41" priority="51"/>
-    <cfRule type="duplicateValues" dxfId="40" priority="52"/>
-    <cfRule type="duplicateValues" dxfId="39" priority="53"/>
-    <cfRule type="duplicateValues" dxfId="38" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="45" priority="48"/>
+    <cfRule type="duplicateValues" dxfId="44" priority="49"/>
+    <cfRule type="duplicateValues" dxfId="43" priority="50"/>
+    <cfRule type="duplicateValues" dxfId="42" priority="51"/>
+    <cfRule type="duplicateValues" dxfId="41" priority="52"/>
+    <cfRule type="duplicateValues" dxfId="40" priority="53"/>
+    <cfRule type="duplicateValues" dxfId="39" priority="54"/>
+    <cfRule type="duplicateValues" dxfId="38" priority="55"/>
     <cfRule type="duplicateValues" dxfId="37" priority="56"/>
     <cfRule type="duplicateValues" dxfId="36" priority="57"/>
     <cfRule type="duplicateValues" dxfId="35" priority="58"/>
@@ -12890,21 +13057,21 @@
   </conditionalFormatting>
   <conditionalFormatting sqref="F58">
     <cfRule type="duplicateValues" dxfId="15" priority="2"/>
-    <cfRule type="duplicateValues" dxfId="14" priority="47"/>
-    <cfRule type="duplicateValues" dxfId="13" priority="33"/>
-    <cfRule type="duplicateValues" dxfId="12" priority="34"/>
-    <cfRule type="duplicateValues" dxfId="11" priority="35"/>
-    <cfRule type="duplicateValues" dxfId="10" priority="36"/>
-    <cfRule type="duplicateValues" dxfId="9" priority="37"/>
-    <cfRule type="duplicateValues" dxfId="8" priority="38"/>
-    <cfRule type="duplicateValues" dxfId="7" priority="39"/>
-    <cfRule type="duplicateValues" dxfId="6" priority="40"/>
-    <cfRule type="duplicateValues" dxfId="5" priority="41"/>
-    <cfRule type="duplicateValues" dxfId="4" priority="42"/>
-    <cfRule type="duplicateValues" dxfId="3" priority="43"/>
-    <cfRule type="duplicateValues" dxfId="2" priority="44"/>
-    <cfRule type="duplicateValues" dxfId="1" priority="45"/>
-    <cfRule type="duplicateValues" dxfId="0" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="14" priority="33"/>
+    <cfRule type="duplicateValues" dxfId="13" priority="34"/>
+    <cfRule type="duplicateValues" dxfId="12" priority="35"/>
+    <cfRule type="duplicateValues" dxfId="11" priority="36"/>
+    <cfRule type="duplicateValues" dxfId="10" priority="37"/>
+    <cfRule type="duplicateValues" dxfId="9" priority="38"/>
+    <cfRule type="duplicateValues" dxfId="8" priority="39"/>
+    <cfRule type="duplicateValues" dxfId="7" priority="40"/>
+    <cfRule type="duplicateValues" dxfId="6" priority="41"/>
+    <cfRule type="duplicateValues" dxfId="5" priority="42"/>
+    <cfRule type="duplicateValues" dxfId="4" priority="43"/>
+    <cfRule type="duplicateValues" dxfId="3" priority="44"/>
+    <cfRule type="duplicateValues" dxfId="2" priority="45"/>
+    <cfRule type="duplicateValues" dxfId="1" priority="46"/>
+    <cfRule type="duplicateValues" dxfId="0" priority="47"/>
   </conditionalFormatting>
   <pageMargins left="0.7" right="0.48" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
   <pageSetup paperSize="9" orientation="portrait" r:id="rId1"/>
